--- a/output_phyto/phyto_Intermediate_bae_2015.xlsx
+++ b/output_phyto/phyto_Intermediate_bae_2015.xlsx
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">10.1016/j.csr.2015.07.010</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/phytoplankton_bae_2015.xlsx</t>
+    <t xml:space="preserve">phytoplankton_bae_2015_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">Mk37_2</t>
   </si>
   <si>
-    <t xml:space="preserve">alkenone unsaturation</t>
+    <t xml:space="preserve">published Uk37 temperature</t>
   </si>
   <si>
     <t xml:space="preserve">WOA 2013</t>
@@ -1792,7 +1792,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1858,12 +1858,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1977,7 +1971,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2076,7 +2070,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2802,7 +2795,7 @@
       <c r="B5" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" t="s">
         <v>272</v>
       </c>
       <c r="D5" t="s">
@@ -2820,8 +2813,8 @@
       <c r="H5" t="n">
         <v>0.0005</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.004</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2838,8 +2831,8 @@
       <c r="N5" t="n">
         <v>-21.9</v>
       </c>
-      <c r="O5" t="e">
-        <v>#N/A</v>
+      <c r="O5" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P5" t="e">
         <v>#N/A</v>
@@ -2851,7 +2844,7 @@
         <v>17</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="e">
         <v>#N/A</v>
@@ -2868,29 +2861,29 @@
       <c r="X5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z5" t="e">
-        <v>#N/A</v>
+      <c r="Y5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA5" t="s">
         <v>278</v>
       </c>
-      <c r="AB5" t="e">
-        <v>#N/A</v>
+      <c r="AB5" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF5" t="e">
-        <v>#N/A</v>
+      <c r="AD5" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG5" t="e">
         <v>#N/A</v>
@@ -2912,7 +2905,7 @@
       <c r="B6" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" t="s">
         <v>272</v>
       </c>
       <c r="D6" t="s">
@@ -2930,8 +2923,8 @@
       <c r="H6" t="n">
         <v>0.0024</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.004</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2948,8 +2941,8 @@
       <c r="N6" t="n">
         <v>-20.6</v>
       </c>
-      <c r="O6" t="e">
-        <v>#N/A</v>
+      <c r="O6" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P6" t="e">
         <v>#N/A</v>
@@ -2961,7 +2954,7 @@
         <v>17.2</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T6" t="e">
         <v>#N/A</v>
@@ -2978,29 +2971,29 @@
       <c r="X6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z6" t="e">
-        <v>#N/A</v>
+      <c r="Y6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA6" t="s">
         <v>281</v>
       </c>
-      <c r="AB6" t="e">
-        <v>#N/A</v>
+      <c r="AB6" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF6" t="e">
-        <v>#N/A</v>
+      <c r="AD6" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG6" t="e">
         <v>#N/A</v>
@@ -3022,7 +3015,7 @@
       <c r="B7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" t="s">
         <v>272</v>
       </c>
       <c r="D7" t="s">
@@ -3040,8 +3033,8 @@
       <c r="H7" t="n">
         <v>0.005</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.004</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -3058,8 +3051,8 @@
       <c r="N7" t="n">
         <v>-21.4</v>
       </c>
-      <c r="O7" t="e">
-        <v>#N/A</v>
+      <c r="O7" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P7" t="e">
         <v>#N/A</v>
@@ -3071,7 +3064,7 @@
         <v>17.2</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T7" t="e">
         <v>#N/A</v>
@@ -3088,29 +3081,29 @@
       <c r="X7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z7" t="e">
-        <v>#N/A</v>
+      <c r="Y7" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA7" t="s">
         <v>281</v>
       </c>
-      <c r="AB7" t="e">
-        <v>#N/A</v>
+      <c r="AB7" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF7" t="e">
-        <v>#N/A</v>
+      <c r="AD7" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG7" t="e">
         <v>#N/A</v>
@@ -3132,7 +3125,7 @@
       <c r="B8" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" t="s">
         <v>272</v>
       </c>
       <c r="D8" t="s">
@@ -3150,8 +3143,8 @@
       <c r="H8" t="n">
         <v>0.0076</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.004</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -3168,8 +3161,8 @@
       <c r="N8" t="n">
         <v>-21.5</v>
       </c>
-      <c r="O8" t="e">
-        <v>#N/A</v>
+      <c r="O8" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P8" t="e">
         <v>#N/A</v>
@@ -3181,7 +3174,7 @@
         <v>16.2</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T8" t="e">
         <v>#N/A</v>
@@ -3198,29 +3191,29 @@
       <c r="X8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z8" t="e">
-        <v>#N/A</v>
+      <c r="Y8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA8" t="s">
         <v>281</v>
       </c>
-      <c r="AB8" t="e">
-        <v>#N/A</v>
+      <c r="AB8" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF8" t="e">
-        <v>#N/A</v>
+      <c r="AD8" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG8" t="e">
         <v>#N/A</v>
@@ -3242,7 +3235,7 @@
       <c r="B9" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" t="s">
         <v>272</v>
       </c>
       <c r="D9" t="s">
@@ -3260,8 +3253,8 @@
       <c r="H9" t="n">
         <v>0.0102</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.004</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -3278,8 +3271,8 @@
       <c r="N9" t="n">
         <v>-22.3</v>
       </c>
-      <c r="O9" t="e">
-        <v>#N/A</v>
+      <c r="O9" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P9" t="e">
         <v>#N/A</v>
@@ -3291,7 +3284,7 @@
         <v>15.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="e">
         <v>#N/A</v>
@@ -3308,29 +3301,29 @@
       <c r="X9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z9" t="e">
-        <v>#N/A</v>
+      <c r="Y9" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA9" t="s">
         <v>281</v>
       </c>
-      <c r="AB9" t="e">
-        <v>#N/A</v>
+      <c r="AB9" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF9" t="e">
-        <v>#N/A</v>
+      <c r="AD9" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG9" t="e">
         <v>#N/A</v>
@@ -3352,7 +3345,7 @@
       <c r="B10" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" t="s">
         <v>272</v>
       </c>
       <c r="D10" t="s">
@@ -3370,8 +3363,8 @@
       <c r="H10" t="n">
         <v>0.0128</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.004</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3388,8 +3381,8 @@
       <c r="N10" t="n">
         <v>-22.2</v>
       </c>
-      <c r="O10" t="e">
-        <v>#N/A</v>
+      <c r="O10" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P10" t="e">
         <v>#N/A</v>
@@ -3401,7 +3394,7 @@
         <v>15.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="e">
         <v>#N/A</v>
@@ -3418,29 +3411,29 @@
       <c r="X10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z10" t="e">
-        <v>#N/A</v>
+      <c r="Y10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA10" t="s">
         <v>281</v>
       </c>
-      <c r="AB10" t="e">
-        <v>#N/A</v>
+      <c r="AB10" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF10" t="e">
-        <v>#N/A</v>
+      <c r="AD10" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG10" t="e">
         <v>#N/A</v>
@@ -3462,7 +3455,7 @@
       <c r="B11" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
       <c r="D11" t="s">
@@ -3480,8 +3473,8 @@
       <c r="H11" t="n">
         <v>0.014</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.004</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3498,8 +3491,8 @@
       <c r="N11" t="n">
         <v>-21.5</v>
       </c>
-      <c r="O11" t="e">
-        <v>#N/A</v>
+      <c r="O11" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P11" t="e">
         <v>#N/A</v>
@@ -3511,7 +3504,7 @@
         <v>17.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T11" t="e">
         <v>#N/A</v>
@@ -3528,29 +3521,29 @@
       <c r="X11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z11" t="e">
-        <v>#N/A</v>
+      <c r="Y11" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA11" t="s">
         <v>281</v>
       </c>
-      <c r="AB11" t="e">
-        <v>#N/A</v>
+      <c r="AB11" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF11" t="e">
-        <v>#N/A</v>
+      <c r="AD11" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG11" t="e">
         <v>#N/A</v>
@@ -3572,7 +3565,7 @@
       <c r="B12" t="s">
         <v>271</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" t="s">
         <v>272</v>
       </c>
       <c r="D12" t="s">
@@ -3590,8 +3583,8 @@
       <c r="H12" t="n">
         <v>0.0152</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.004</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3608,8 +3601,8 @@
       <c r="N12" t="n">
         <v>-21.4</v>
       </c>
-      <c r="O12" t="e">
-        <v>#N/A</v>
+      <c r="O12" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P12" t="e">
         <v>#N/A</v>
@@ -3621,7 +3614,7 @@
         <v>15.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="e">
         <v>#N/A</v>
@@ -3638,29 +3631,29 @@
       <c r="X12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z12" t="e">
-        <v>#N/A</v>
+      <c r="Y12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA12" t="s">
         <v>281</v>
       </c>
-      <c r="AB12" t="e">
-        <v>#N/A</v>
+      <c r="AB12" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF12" t="e">
-        <v>#N/A</v>
+      <c r="AD12" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG12" t="e">
         <v>#N/A</v>
@@ -3682,7 +3675,7 @@
       <c r="B13" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" t="s">
         <v>272</v>
       </c>
       <c r="D13" t="s">
@@ -3700,8 +3693,8 @@
       <c r="H13" t="n">
         <v>0.0164</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.004</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3718,8 +3711,8 @@
       <c r="N13" t="n">
         <v>-21.8</v>
       </c>
-      <c r="O13" t="e">
-        <v>#N/A</v>
+      <c r="O13" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P13" t="e">
         <v>#N/A</v>
@@ -3731,7 +3724,7 @@
         <v>16.2</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T13" t="e">
         <v>#N/A</v>
@@ -3748,29 +3741,29 @@
       <c r="X13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z13" t="e">
-        <v>#N/A</v>
+      <c r="Y13" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA13" t="s">
         <v>281</v>
       </c>
-      <c r="AB13" t="e">
-        <v>#N/A</v>
+      <c r="AB13" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF13" t="e">
-        <v>#N/A</v>
+      <c r="AD13" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG13" t="e">
         <v>#N/A</v>
@@ -3792,7 +3785,7 @@
       <c r="B14" t="s">
         <v>271</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" t="s">
         <v>272</v>
       </c>
       <c r="D14" t="s">
@@ -3810,8 +3803,8 @@
       <c r="H14" t="n">
         <v>0.0176</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.004</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3828,8 +3821,8 @@
       <c r="N14" t="n">
         <v>-21.5</v>
       </c>
-      <c r="O14" t="e">
-        <v>#N/A</v>
+      <c r="O14" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P14" t="e">
         <v>#N/A</v>
@@ -3841,7 +3834,7 @@
         <v>17.1</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" t="e">
         <v>#N/A</v>
@@ -3858,29 +3851,29 @@
       <c r="X14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z14" t="e">
-        <v>#N/A</v>
+      <c r="Y14" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA14" t="s">
         <v>281</v>
       </c>
-      <c r="AB14" t="e">
-        <v>#N/A</v>
+      <c r="AB14" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF14" t="e">
-        <v>#N/A</v>
+      <c r="AD14" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG14" t="e">
         <v>#N/A</v>
@@ -3902,7 +3895,7 @@
       <c r="B15" t="s">
         <v>271</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" t="s">
         <v>272</v>
       </c>
       <c r="D15" t="s">
@@ -3920,8 +3913,8 @@
       <c r="H15" t="n">
         <v>0.0372</v>
       </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+      <c r="I15" t="n">
+        <v>0.004</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3938,8 +3931,8 @@
       <c r="N15" t="n">
         <v>-21.8</v>
       </c>
-      <c r="O15" t="e">
-        <v>#N/A</v>
+      <c r="O15" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P15" t="e">
         <v>#N/A</v>
@@ -3951,7 +3944,7 @@
         <v>12.8</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T15" t="e">
         <v>#N/A</v>
@@ -3968,29 +3961,29 @@
       <c r="X15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z15" t="e">
-        <v>#N/A</v>
+      <c r="Y15" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA15" t="s">
         <v>281</v>
       </c>
-      <c r="AB15" t="e">
-        <v>#N/A</v>
+      <c r="AB15" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF15" t="e">
-        <v>#N/A</v>
+      <c r="AD15" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG15" t="e">
         <v>#N/A</v>
@@ -4012,7 +4005,7 @@
       <c r="B16" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" t="s">
         <v>272</v>
       </c>
       <c r="D16" t="s">
@@ -4030,8 +4023,8 @@
       <c r="H16" t="n">
         <v>0.0394</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.004</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -4048,8 +4041,8 @@
       <c r="N16" t="n">
         <v>-19.4</v>
       </c>
-      <c r="O16" t="e">
-        <v>#N/A</v>
+      <c r="O16" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P16" t="e">
         <v>#N/A</v>
@@ -4061,7 +4054,7 @@
         <v>11.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" t="e">
         <v>#N/A</v>
@@ -4078,29 +4071,29 @@
       <c r="X16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z16" t="e">
-        <v>#N/A</v>
+      <c r="Y16" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA16" t="s">
         <v>281</v>
       </c>
-      <c r="AB16" t="e">
-        <v>#N/A</v>
+      <c r="AB16" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF16" t="e">
-        <v>#N/A</v>
+      <c r="AD16" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG16" t="e">
         <v>#N/A</v>
@@ -4122,7 +4115,7 @@
       <c r="B17" t="s">
         <v>271</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" t="s">
         <v>272</v>
       </c>
       <c r="D17" t="s">
@@ -4140,8 +4133,8 @@
       <c r="H17" t="n">
         <v>0.041</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.004</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -4158,8 +4151,8 @@
       <c r="N17" t="n">
         <v>-21.8</v>
       </c>
-      <c r="O17" t="e">
-        <v>#N/A</v>
+      <c r="O17" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P17" t="e">
         <v>#N/A</v>
@@ -4171,7 +4164,7 @@
         <v>10.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T17" t="e">
         <v>#N/A</v>
@@ -4188,29 +4181,29 @@
       <c r="X17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z17" t="e">
-        <v>#N/A</v>
+      <c r="Y17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA17" t="s">
         <v>281</v>
       </c>
-      <c r="AB17" t="e">
-        <v>#N/A</v>
+      <c r="AB17" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF17" t="e">
-        <v>#N/A</v>
+      <c r="AD17" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG17" t="e">
         <v>#N/A</v>
@@ -4232,7 +4225,7 @@
       <c r="B18" t="s">
         <v>271</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" t="s">
         <v>272</v>
       </c>
       <c r="D18" t="s">
@@ -4250,8 +4243,8 @@
       <c r="H18" t="n">
         <v>0.0421</v>
       </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+      <c r="I18" t="n">
+        <v>0.004</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -4268,8 +4261,8 @@
       <c r="N18" t="n">
         <v>-22.2</v>
       </c>
-      <c r="O18" t="e">
-        <v>#N/A</v>
+      <c r="O18" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P18" t="e">
         <v>#N/A</v>
@@ -4281,7 +4274,7 @@
         <v>13.2</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T18" t="e">
         <v>#N/A</v>
@@ -4298,29 +4291,29 @@
       <c r="X18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z18" t="e">
-        <v>#N/A</v>
+      <c r="Y18" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA18" t="s">
         <v>281</v>
       </c>
-      <c r="AB18" t="e">
-        <v>#N/A</v>
+      <c r="AB18" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF18" t="e">
-        <v>#N/A</v>
+      <c r="AD18" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG18" t="e">
         <v>#N/A</v>
@@ -4342,7 +4335,7 @@
       <c r="B19" t="s">
         <v>271</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" t="s">
         <v>272</v>
       </c>
       <c r="D19" t="s">
@@ -4360,8 +4353,8 @@
       <c r="H19" t="n">
         <v>0.0432</v>
       </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+      <c r="I19" t="n">
+        <v>0.004</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -4378,8 +4371,8 @@
       <c r="N19" t="n">
         <v>-19.9</v>
       </c>
-      <c r="O19" t="e">
-        <v>#N/A</v>
+      <c r="O19" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P19" t="e">
         <v>#N/A</v>
@@ -4391,7 +4384,7 @@
         <v>11.6</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T19" t="e">
         <v>#N/A</v>
@@ -4408,29 +4401,29 @@
       <c r="X19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z19" t="e">
-        <v>#N/A</v>
+      <c r="Y19" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA19" t="s">
         <v>281</v>
       </c>
-      <c r="AB19" t="e">
-        <v>#N/A</v>
+      <c r="AB19" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF19" t="e">
-        <v>#N/A</v>
+      <c r="AD19" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG19" t="e">
         <v>#N/A</v>
@@ -4452,7 +4445,7 @@
       <c r="B20" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" t="s">
         <v>272</v>
       </c>
       <c r="D20" t="s">
@@ -4470,8 +4463,8 @@
       <c r="H20" t="n">
         <v>0.0453</v>
       </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+      <c r="I20" t="n">
+        <v>0.004</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -4488,8 +4481,8 @@
       <c r="N20" t="n">
         <v>-19.6</v>
       </c>
-      <c r="O20" t="e">
-        <v>#N/A</v>
+      <c r="O20" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P20" t="e">
         <v>#N/A</v>
@@ -4501,7 +4494,7 @@
         <v>10.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T20" t="e">
         <v>#N/A</v>
@@ -4518,29 +4511,29 @@
       <c r="X20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z20" t="e">
-        <v>#N/A</v>
+      <c r="Y20" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA20" t="s">
         <v>281</v>
       </c>
-      <c r="AB20" t="e">
-        <v>#N/A</v>
+      <c r="AB20" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF20" t="e">
-        <v>#N/A</v>
+      <c r="AD20" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG20" t="e">
         <v>#N/A</v>
@@ -4562,7 +4555,7 @@
       <c r="B21" t="s">
         <v>271</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" t="s">
         <v>272</v>
       </c>
       <c r="D21" t="s">
@@ -4580,8 +4573,8 @@
       <c r="H21" t="n">
         <v>0.0509</v>
       </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+      <c r="I21" t="n">
+        <v>0.004</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -4598,8 +4591,8 @@
       <c r="N21" t="n">
         <v>-22.8</v>
       </c>
-      <c r="O21" t="e">
-        <v>#N/A</v>
+      <c r="O21" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P21" t="e">
         <v>#N/A</v>
@@ -4611,7 +4604,7 @@
         <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T21" t="e">
         <v>#N/A</v>
@@ -4628,29 +4621,29 @@
       <c r="X21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z21" t="e">
-        <v>#N/A</v>
+      <c r="Y21" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA21" t="s">
         <v>281</v>
       </c>
-      <c r="AB21" t="e">
-        <v>#N/A</v>
+      <c r="AB21" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF21" t="e">
-        <v>#N/A</v>
+      <c r="AD21" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG21" t="e">
         <v>#N/A</v>
@@ -4672,7 +4665,7 @@
       <c r="B22" t="s">
         <v>271</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" t="s">
         <v>272</v>
       </c>
       <c r="D22" t="s">
@@ -4690,8 +4683,8 @@
       <c r="H22" t="n">
         <v>0.0716</v>
       </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+      <c r="I22" t="n">
+        <v>0.004</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -4708,8 +4701,8 @@
       <c r="N22" t="n">
         <v>-22.8</v>
       </c>
-      <c r="O22" t="e">
-        <v>#N/A</v>
+      <c r="O22" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P22" t="e">
         <v>#N/A</v>
@@ -4721,7 +4714,7 @@
         <v>12.8</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T22" t="e">
         <v>#N/A</v>
@@ -4738,29 +4731,29 @@
       <c r="X22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z22" t="e">
-        <v>#N/A</v>
+      <c r="Y22" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA22" t="s">
         <v>281</v>
       </c>
-      <c r="AB22" t="e">
-        <v>#N/A</v>
+      <c r="AB22" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF22" t="e">
-        <v>#N/A</v>
+      <c r="AD22" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG22" t="e">
         <v>#N/A</v>
@@ -4782,7 +4775,7 @@
       <c r="B23" t="s">
         <v>271</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" t="s">
         <v>272</v>
       </c>
       <c r="D23" t="s">
@@ -4800,8 +4793,8 @@
       <c r="H23" t="n">
         <v>0.0725</v>
       </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+      <c r="I23" t="n">
+        <v>0.004</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -4818,8 +4811,8 @@
       <c r="N23" t="n">
         <v>-22.3</v>
       </c>
-      <c r="O23" t="e">
-        <v>#N/A</v>
+      <c r="O23" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P23" t="e">
         <v>#N/A</v>
@@ -4831,7 +4824,7 @@
         <v>13.1</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T23" t="e">
         <v>#N/A</v>
@@ -4848,29 +4841,29 @@
       <c r="X23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z23" t="e">
-        <v>#N/A</v>
+      <c r="Y23" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA23" t="s">
         <v>281</v>
       </c>
-      <c r="AB23" t="e">
-        <v>#N/A</v>
+      <c r="AB23" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF23" t="e">
-        <v>#N/A</v>
+      <c r="AD23" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG23" t="e">
         <v>#N/A</v>
@@ -4892,7 +4885,7 @@
       <c r="B24" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" t="s">
         <v>272</v>
       </c>
       <c r="D24" t="s">
@@ -4910,8 +4903,8 @@
       <c r="H24" t="n">
         <v>0.0735</v>
       </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+      <c r="I24" t="n">
+        <v>0.004</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -4928,8 +4921,8 @@
       <c r="N24" t="n">
         <v>-21.9</v>
       </c>
-      <c r="O24" t="e">
-        <v>#N/A</v>
+      <c r="O24" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P24" t="e">
         <v>#N/A</v>
@@ -4941,7 +4934,7 @@
         <v>13.6</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T24" t="e">
         <v>#N/A</v>
@@ -4958,29 +4951,29 @@
       <c r="X24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z24" t="e">
-        <v>#N/A</v>
+      <c r="Y24" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA24" t="s">
         <v>281</v>
       </c>
-      <c r="AB24" t="e">
-        <v>#N/A</v>
+      <c r="AB24" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF24" t="e">
-        <v>#N/A</v>
+      <c r="AD24" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG24" t="e">
         <v>#N/A</v>
@@ -5002,7 +4995,7 @@
       <c r="B25" t="s">
         <v>271</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" t="s">
         <v>272</v>
       </c>
       <c r="D25" t="s">
@@ -5020,8 +5013,8 @@
       <c r="H25" t="n">
         <v>0.0765</v>
       </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+      <c r="I25" t="n">
+        <v>0.004</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -5038,8 +5031,8 @@
       <c r="N25" t="n">
         <v>-23.1</v>
       </c>
-      <c r="O25" t="e">
-        <v>#N/A</v>
+      <c r="O25" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P25" t="e">
         <v>#N/A</v>
@@ -5051,7 +5044,7 @@
         <v>15.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T25" t="e">
         <v>#N/A</v>
@@ -5068,29 +5061,29 @@
       <c r="X25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z25" t="e">
-        <v>#N/A</v>
+      <c r="Y25" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA25" t="s">
         <v>281</v>
       </c>
-      <c r="AB25" t="e">
-        <v>#N/A</v>
+      <c r="AB25" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" t="e">
-        <v>#N/A</v>
+      <c r="AD25" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG25" t="e">
         <v>#N/A</v>
@@ -5112,7 +5105,7 @@
       <c r="B26" t="s">
         <v>271</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" t="s">
         <v>272</v>
       </c>
       <c r="D26" t="s">
@@ -5130,8 +5123,8 @@
       <c r="H26" t="n">
         <v>0.0774</v>
       </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+      <c r="I26" t="n">
+        <v>0.004</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -5148,8 +5141,8 @@
       <c r="N26" t="n">
         <v>-22.3</v>
       </c>
-      <c r="O26" t="e">
-        <v>#N/A</v>
+      <c r="O26" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P26" t="e">
         <v>#N/A</v>
@@ -5161,7 +5154,7 @@
         <v>13.3</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="e">
         <v>#N/A</v>
@@ -5178,29 +5171,29 @@
       <c r="X26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z26" t="e">
-        <v>#N/A</v>
+      <c r="Y26" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA26" t="s">
         <v>281</v>
       </c>
-      <c r="AB26" t="e">
-        <v>#N/A</v>
+      <c r="AB26" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF26" t="e">
-        <v>#N/A</v>
+      <c r="AD26" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG26" t="e">
         <v>#N/A</v>
@@ -5222,7 +5215,7 @@
       <c r="B27" t="s">
         <v>271</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C27" t="s">
         <v>272</v>
       </c>
       <c r="D27" t="s">
@@ -5240,8 +5233,8 @@
       <c r="H27" t="n">
         <v>0.0783</v>
       </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+      <c r="I27" t="n">
+        <v>0.004</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -5258,8 +5251,8 @@
       <c r="N27" t="n">
         <v>-21.8</v>
       </c>
-      <c r="O27" t="e">
-        <v>#N/A</v>
+      <c r="O27" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P27" t="e">
         <v>#N/A</v>
@@ -5271,7 +5264,7 @@
         <v>13.7</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T27" t="e">
         <v>#N/A</v>
@@ -5288,29 +5281,29 @@
       <c r="X27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z27" t="e">
-        <v>#N/A</v>
+      <c r="Y27" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA27" t="s">
         <v>281</v>
       </c>
-      <c r="AB27" t="e">
-        <v>#N/A</v>
+      <c r="AB27" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF27" t="e">
-        <v>#N/A</v>
+      <c r="AD27" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG27" t="e">
         <v>#N/A</v>
@@ -5332,7 +5325,7 @@
       <c r="B28" t="s">
         <v>271</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" t="s">
         <v>272</v>
       </c>
       <c r="D28" t="s">
@@ -5350,8 +5343,8 @@
       <c r="H28" t="n">
         <v>0.0792</v>
       </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+      <c r="I28" t="n">
+        <v>0.004</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -5368,8 +5361,8 @@
       <c r="N28" t="n">
         <v>-21.8</v>
       </c>
-      <c r="O28" t="e">
-        <v>#N/A</v>
+      <c r="O28" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P28" t="e">
         <v>#N/A</v>
@@ -5381,7 +5374,7 @@
         <v>13.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T28" t="e">
         <v>#N/A</v>
@@ -5398,29 +5391,29 @@
       <c r="X28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z28" t="e">
-        <v>#N/A</v>
+      <c r="Y28" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA28" t="s">
         <v>281</v>
       </c>
-      <c r="AB28" t="e">
-        <v>#N/A</v>
+      <c r="AB28" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF28" t="e">
-        <v>#N/A</v>
+      <c r="AD28" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG28" t="e">
         <v>#N/A</v>
@@ -5442,7 +5435,7 @@
       <c r="B29" t="s">
         <v>271</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" t="s">
         <v>272</v>
       </c>
       <c r="D29" t="s">
@@ -5460,8 +5453,8 @@
       <c r="H29" t="n">
         <v>0.0809</v>
       </c>
-      <c r="I29" t="e">
-        <v>#N/A</v>
+      <c r="I29" t="n">
+        <v>0.004</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -5478,8 +5471,8 @@
       <c r="N29" t="n">
         <v>-21.6</v>
       </c>
-      <c r="O29" t="e">
-        <v>#N/A</v>
+      <c r="O29" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P29" t="e">
         <v>#N/A</v>
@@ -5491,7 +5484,7 @@
         <v>15.3</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T29" t="e">
         <v>#N/A</v>
@@ -5508,29 +5501,29 @@
       <c r="X29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z29" t="e">
-        <v>#N/A</v>
+      <c r="Y29" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA29" t="s">
         <v>281</v>
       </c>
-      <c r="AB29" t="e">
-        <v>#N/A</v>
+      <c r="AB29" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF29" t="e">
-        <v>#N/A</v>
+      <c r="AD29" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG29" t="e">
         <v>#N/A</v>
@@ -5552,7 +5545,7 @@
       <c r="B30" t="s">
         <v>271</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" t="s">
         <v>272</v>
       </c>
       <c r="D30" t="s">
@@ -5570,8 +5563,8 @@
       <c r="H30" t="n">
         <v>0.0818</v>
       </c>
-      <c r="I30" t="e">
-        <v>#N/A</v>
+      <c r="I30" t="n">
+        <v>0.004</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -5588,8 +5581,8 @@
       <c r="N30" t="n">
         <v>-22.1</v>
       </c>
-      <c r="O30" t="e">
-        <v>#N/A</v>
+      <c r="O30" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P30" t="e">
         <v>#N/A</v>
@@ -5601,7 +5594,7 @@
         <v>15.6</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T30" t="e">
         <v>#N/A</v>
@@ -5618,29 +5611,29 @@
       <c r="X30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z30" t="e">
-        <v>#N/A</v>
+      <c r="Y30" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA30" t="s">
         <v>281</v>
       </c>
-      <c r="AB30" t="e">
-        <v>#N/A</v>
+      <c r="AB30" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF30" t="e">
-        <v>#N/A</v>
+      <c r="AD30" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG30" t="e">
         <v>#N/A</v>
@@ -5662,7 +5655,7 @@
       <c r="B31" t="s">
         <v>271</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" t="s">
         <v>272</v>
       </c>
       <c r="D31" t="s">
@@ -5680,8 +5673,8 @@
       <c r="H31" t="n">
         <v>0.0827</v>
       </c>
-      <c r="I31" t="e">
-        <v>#N/A</v>
+      <c r="I31" t="n">
+        <v>0.004</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -5698,8 +5691,8 @@
       <c r="N31" t="n">
         <v>-21.1</v>
       </c>
-      <c r="O31" t="e">
-        <v>#N/A</v>
+      <c r="O31" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P31" t="e">
         <v>#N/A</v>
@@ -5711,7 +5704,7 @@
         <v>15.6</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="e">
         <v>#N/A</v>
@@ -5728,29 +5721,29 @@
       <c r="X31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z31" t="e">
-        <v>#N/A</v>
+      <c r="Y31" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA31" t="s">
         <v>281</v>
       </c>
-      <c r="AB31" t="e">
-        <v>#N/A</v>
+      <c r="AB31" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF31" t="e">
-        <v>#N/A</v>
+      <c r="AD31" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG31" t="e">
         <v>#N/A</v>
@@ -5772,7 +5765,7 @@
       <c r="B32" t="s">
         <v>271</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" t="s">
         <v>272</v>
       </c>
       <c r="D32" t="s">
@@ -5790,8 +5783,8 @@
       <c r="H32" t="n">
         <v>0.0836</v>
       </c>
-      <c r="I32" t="e">
-        <v>#N/A</v>
+      <c r="I32" t="n">
+        <v>0.004</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -5808,8 +5801,8 @@
       <c r="N32" t="n">
         <v>-22</v>
       </c>
-      <c r="O32" t="e">
-        <v>#N/A</v>
+      <c r="O32" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P32" t="e">
         <v>#N/A</v>
@@ -5821,7 +5814,7 @@
         <v>15.4</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T32" t="e">
         <v>#N/A</v>
@@ -5838,29 +5831,29 @@
       <c r="X32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z32" t="e">
-        <v>#N/A</v>
+      <c r="Y32" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA32" t="s">
         <v>281</v>
       </c>
-      <c r="AB32" t="e">
-        <v>#N/A</v>
+      <c r="AB32" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF32" t="e">
-        <v>#N/A</v>
+      <c r="AD32" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG32" t="e">
         <v>#N/A</v>
@@ -5882,7 +5875,7 @@
       <c r="B33" t="s">
         <v>271</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" t="s">
         <v>272</v>
       </c>
       <c r="D33" t="s">
@@ -5900,8 +5893,8 @@
       <c r="H33" t="n">
         <v>0.0845</v>
       </c>
-      <c r="I33" t="e">
-        <v>#N/A</v>
+      <c r="I33" t="n">
+        <v>0.004</v>
       </c>
       <c r="J33" t="e">
         <v>#N/A</v>
@@ -5918,8 +5911,8 @@
       <c r="N33" t="n">
         <v>-22.4</v>
       </c>
-      <c r="O33" t="e">
-        <v>#N/A</v>
+      <c r="O33" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P33" t="e">
         <v>#N/A</v>
@@ -5931,7 +5924,7 @@
         <v>15.7</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T33" t="e">
         <v>#N/A</v>
@@ -5948,29 +5941,29 @@
       <c r="X33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z33" t="e">
-        <v>#N/A</v>
+      <c r="Y33" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA33" t="s">
         <v>281</v>
       </c>
-      <c r="AB33" t="e">
-        <v>#N/A</v>
+      <c r="AB33" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF33" t="e">
-        <v>#N/A</v>
+      <c r="AD33" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG33" t="e">
         <v>#N/A</v>
@@ -5992,7 +5985,7 @@
       <c r="B34" t="s">
         <v>271</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C34" t="s">
         <v>272</v>
       </c>
       <c r="D34" t="s">
@@ -6010,8 +6003,8 @@
       <c r="H34" t="n">
         <v>0.0853</v>
       </c>
-      <c r="I34" t="e">
-        <v>#N/A</v>
+      <c r="I34" t="n">
+        <v>0.004</v>
       </c>
       <c r="J34" t="e">
         <v>#N/A</v>
@@ -6028,8 +6021,8 @@
       <c r="N34" t="n">
         <v>-22.1</v>
       </c>
-      <c r="O34" t="e">
-        <v>#N/A</v>
+      <c r="O34" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P34" t="e">
         <v>#N/A</v>
@@ -6041,7 +6034,7 @@
         <v>15.2</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T34" t="e">
         <v>#N/A</v>
@@ -6058,29 +6051,29 @@
       <c r="X34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z34" t="e">
-        <v>#N/A</v>
+      <c r="Y34" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA34" t="s">
         <v>281</v>
       </c>
-      <c r="AB34" t="e">
-        <v>#N/A</v>
+      <c r="AB34" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF34" t="e">
-        <v>#N/A</v>
+      <c r="AD34" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG34" t="e">
         <v>#N/A</v>
@@ -6102,7 +6095,7 @@
       <c r="B35" t="s">
         <v>271</v>
       </c>
-      <c r="C35" s="34" t="s">
+      <c r="C35" t="s">
         <v>272</v>
       </c>
       <c r="D35" t="s">
@@ -6120,8 +6113,8 @@
       <c r="H35" t="n">
         <v>0.0862</v>
       </c>
-      <c r="I35" t="e">
-        <v>#N/A</v>
+      <c r="I35" t="n">
+        <v>0.004</v>
       </c>
       <c r="J35" t="e">
         <v>#N/A</v>
@@ -6138,8 +6131,8 @@
       <c r="N35" t="n">
         <v>-22.3</v>
       </c>
-      <c r="O35" t="e">
-        <v>#N/A</v>
+      <c r="O35" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P35" t="e">
         <v>#N/A</v>
@@ -6151,7 +6144,7 @@
         <v>15</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T35" t="e">
         <v>#N/A</v>
@@ -6168,29 +6161,29 @@
       <c r="X35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z35" t="e">
-        <v>#N/A</v>
+      <c r="Y35" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA35" t="s">
         <v>281</v>
       </c>
-      <c r="AB35" t="e">
-        <v>#N/A</v>
+      <c r="AB35" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF35" t="e">
-        <v>#N/A</v>
+      <c r="AD35" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG35" t="e">
         <v>#N/A</v>
@@ -6212,7 +6205,7 @@
       <c r="B36" t="s">
         <v>271</v>
       </c>
-      <c r="C36" s="34" t="s">
+      <c r="C36" t="s">
         <v>272</v>
       </c>
       <c r="D36" t="s">
@@ -6230,8 +6223,8 @@
       <c r="H36" t="n">
         <v>0.0871</v>
       </c>
-      <c r="I36" t="e">
-        <v>#N/A</v>
+      <c r="I36" t="n">
+        <v>0.004</v>
       </c>
       <c r="J36" t="e">
         <v>#N/A</v>
@@ -6248,8 +6241,8 @@
       <c r="N36" t="n">
         <v>-22.9</v>
       </c>
-      <c r="O36" t="e">
-        <v>#N/A</v>
+      <c r="O36" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P36" t="e">
         <v>#N/A</v>
@@ -6261,7 +6254,7 @@
         <v>14.8</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T36" t="e">
         <v>#N/A</v>
@@ -6278,29 +6271,29 @@
       <c r="X36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z36" t="e">
-        <v>#N/A</v>
+      <c r="Y36" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA36" t="s">
         <v>281</v>
       </c>
-      <c r="AB36" t="e">
-        <v>#N/A</v>
+      <c r="AB36" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF36" t="e">
-        <v>#N/A</v>
+      <c r="AD36" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG36" t="e">
         <v>#N/A</v>
@@ -6322,7 +6315,7 @@
       <c r="B37" t="s">
         <v>271</v>
       </c>
-      <c r="C37" s="34" t="s">
+      <c r="C37" t="s">
         <v>272</v>
       </c>
       <c r="D37" t="s">
@@ -6340,8 +6333,8 @@
       <c r="H37" t="n">
         <v>0.0903</v>
       </c>
-      <c r="I37" t="e">
-        <v>#N/A</v>
+      <c r="I37" t="n">
+        <v>0.004</v>
       </c>
       <c r="J37" t="e">
         <v>#N/A</v>
@@ -6358,8 +6351,8 @@
       <c r="N37" t="n">
         <v>-21.9</v>
       </c>
-      <c r="O37" t="e">
-        <v>#N/A</v>
+      <c r="O37" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P37" t="e">
         <v>#N/A</v>
@@ -6371,7 +6364,7 @@
         <v>15.2</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T37" t="e">
         <v>#N/A</v>
@@ -6388,29 +6381,29 @@
       <c r="X37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z37" t="e">
-        <v>#N/A</v>
+      <c r="Y37" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA37" t="s">
         <v>281</v>
       </c>
-      <c r="AB37" t="e">
-        <v>#N/A</v>
+      <c r="AB37" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF37" t="e">
-        <v>#N/A</v>
+      <c r="AD37" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG37" t="e">
         <v>#N/A</v>
@@ -6432,7 +6425,7 @@
       <c r="B38" t="s">
         <v>271</v>
       </c>
-      <c r="C38" s="34" t="s">
+      <c r="C38" t="s">
         <v>272</v>
       </c>
       <c r="D38" t="s">
@@ -6450,8 +6443,8 @@
       <c r="H38" t="n">
         <v>0.0916</v>
       </c>
-      <c r="I38" t="e">
-        <v>#N/A</v>
+      <c r="I38" t="n">
+        <v>0.004</v>
       </c>
       <c r="J38" t="e">
         <v>#N/A</v>
@@ -6468,8 +6461,8 @@
       <c r="N38" t="n">
         <v>-23</v>
       </c>
-      <c r="O38" t="e">
-        <v>#N/A</v>
+      <c r="O38" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P38" t="e">
         <v>#N/A</v>
@@ -6481,7 +6474,7 @@
         <v>15.2</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T38" t="e">
         <v>#N/A</v>
@@ -6498,29 +6491,29 @@
       <c r="X38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z38" t="e">
-        <v>#N/A</v>
+      <c r="Y38" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA38" t="s">
         <v>281</v>
       </c>
-      <c r="AB38" t="e">
-        <v>#N/A</v>
+      <c r="AB38" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF38" t="e">
-        <v>#N/A</v>
+      <c r="AD38" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG38" t="e">
         <v>#N/A</v>
@@ -6542,7 +6535,7 @@
       <c r="B39" t="s">
         <v>271</v>
       </c>
-      <c r="C39" s="34" t="s">
+      <c r="C39" t="s">
         <v>272</v>
       </c>
       <c r="D39" t="s">
@@ -6560,8 +6553,8 @@
       <c r="H39" t="n">
         <v>0.093</v>
       </c>
-      <c r="I39" t="e">
-        <v>#N/A</v>
+      <c r="I39" t="n">
+        <v>0.004</v>
       </c>
       <c r="J39" t="e">
         <v>#N/A</v>
@@ -6578,8 +6571,8 @@
       <c r="N39" t="n">
         <v>-22.5</v>
       </c>
-      <c r="O39" t="e">
-        <v>#N/A</v>
+      <c r="O39" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P39" t="e">
         <v>#N/A</v>
@@ -6591,7 +6584,7 @@
         <v>15.6</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T39" t="e">
         <v>#N/A</v>
@@ -6608,29 +6601,29 @@
       <c r="X39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z39" t="e">
-        <v>#N/A</v>
+      <c r="Y39" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA39" t="s">
         <v>281</v>
       </c>
-      <c r="AB39" t="e">
-        <v>#N/A</v>
+      <c r="AB39" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF39" t="e">
-        <v>#N/A</v>
+      <c r="AD39" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG39" t="e">
         <v>#N/A</v>
@@ -6652,7 +6645,7 @@
       <c r="B40" t="s">
         <v>271</v>
       </c>
-      <c r="C40" s="34" t="s">
+      <c r="C40" t="s">
         <v>272</v>
       </c>
       <c r="D40" t="s">
@@ -6670,8 +6663,8 @@
       <c r="H40" t="n">
         <v>0.0943</v>
       </c>
-      <c r="I40" t="e">
-        <v>#N/A</v>
+      <c r="I40" t="n">
+        <v>0.004</v>
       </c>
       <c r="J40" t="e">
         <v>#N/A</v>
@@ -6688,8 +6681,8 @@
       <c r="N40" t="n">
         <v>-22.9</v>
       </c>
-      <c r="O40" t="e">
-        <v>#N/A</v>
+      <c r="O40" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P40" t="e">
         <v>#N/A</v>
@@ -6701,7 +6694,7 @@
         <v>16</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T40" t="e">
         <v>#N/A</v>
@@ -6718,29 +6711,29 @@
       <c r="X40" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z40" t="e">
-        <v>#N/A</v>
+      <c r="Y40" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA40" t="s">
         <v>281</v>
       </c>
-      <c r="AB40" t="e">
-        <v>#N/A</v>
+      <c r="AB40" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC40" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF40" t="e">
-        <v>#N/A</v>
+      <c r="AD40" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG40" t="e">
         <v>#N/A</v>
@@ -6762,7 +6755,7 @@
       <c r="B41" t="s">
         <v>271</v>
       </c>
-      <c r="C41" s="34" t="s">
+      <c r="C41" t="s">
         <v>272</v>
       </c>
       <c r="D41" t="s">
@@ -6780,8 +6773,8 @@
       <c r="H41" t="n">
         <v>0.0956</v>
       </c>
-      <c r="I41" t="e">
-        <v>#N/A</v>
+      <c r="I41" t="n">
+        <v>0.004</v>
       </c>
       <c r="J41" t="e">
         <v>#N/A</v>
@@ -6798,8 +6791,8 @@
       <c r="N41" t="n">
         <v>-22.1</v>
       </c>
-      <c r="O41" t="e">
-        <v>#N/A</v>
+      <c r="O41" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P41" t="e">
         <v>#N/A</v>
@@ -6811,7 +6804,7 @@
         <v>16.6</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="e">
         <v>#N/A</v>
@@ -6828,29 +6821,29 @@
       <c r="X41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z41" t="e">
-        <v>#N/A</v>
+      <c r="Y41" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA41" t="s">
         <v>281</v>
       </c>
-      <c r="AB41" t="e">
-        <v>#N/A</v>
+      <c r="AB41" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF41" t="e">
-        <v>#N/A</v>
+      <c r="AD41" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG41" t="e">
         <v>#N/A</v>
@@ -6872,7 +6865,7 @@
       <c r="B42" t="s">
         <v>271</v>
       </c>
-      <c r="C42" s="34" t="s">
+      <c r="C42" t="s">
         <v>272</v>
       </c>
       <c r="D42" t="s">
@@ -6890,8 +6883,8 @@
       <c r="H42" t="n">
         <v>0.0969</v>
       </c>
-      <c r="I42" t="e">
-        <v>#N/A</v>
+      <c r="I42" t="n">
+        <v>0.004</v>
       </c>
       <c r="J42" t="e">
         <v>#N/A</v>
@@ -6908,8 +6901,8 @@
       <c r="N42" t="n">
         <v>-22.6</v>
       </c>
-      <c r="O42" t="e">
-        <v>#N/A</v>
+      <c r="O42" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P42" t="e">
         <v>#N/A</v>
@@ -6921,7 +6914,7 @@
         <v>17.3</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T42" t="e">
         <v>#N/A</v>
@@ -6938,29 +6931,29 @@
       <c r="X42" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z42" t="e">
-        <v>#N/A</v>
+      <c r="Y42" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA42" t="s">
         <v>281</v>
       </c>
-      <c r="AB42" t="e">
-        <v>#N/A</v>
+      <c r="AB42" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC42" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF42" t="e">
-        <v>#N/A</v>
+      <c r="AD42" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG42" t="e">
         <v>#N/A</v>
@@ -6982,7 +6975,7 @@
       <c r="B43" t="s">
         <v>271</v>
       </c>
-      <c r="C43" s="34" t="s">
+      <c r="C43" t="s">
         <v>272</v>
       </c>
       <c r="D43" t="s">
@@ -7000,8 +6993,8 @@
       <c r="H43" t="n">
         <v>0.0982</v>
       </c>
-      <c r="I43" t="e">
-        <v>#N/A</v>
+      <c r="I43" t="n">
+        <v>0.004</v>
       </c>
       <c r="J43" t="e">
         <v>#N/A</v>
@@ -7018,8 +7011,8 @@
       <c r="N43" t="n">
         <v>-22.6</v>
       </c>
-      <c r="O43" t="e">
-        <v>#N/A</v>
+      <c r="O43" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P43" t="e">
         <v>#N/A</v>
@@ -7031,7 +7024,7 @@
         <v>17.7</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T43" t="e">
         <v>#N/A</v>
@@ -7048,29 +7041,29 @@
       <c r="X43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z43" t="e">
-        <v>#N/A</v>
+      <c r="Y43" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA43" t="s">
         <v>281</v>
       </c>
-      <c r="AB43" t="e">
-        <v>#N/A</v>
+      <c r="AB43" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF43" t="e">
-        <v>#N/A</v>
+      <c r="AD43" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG43" t="e">
         <v>#N/A</v>
@@ -7092,7 +7085,7 @@
       <c r="B44" t="s">
         <v>271</v>
       </c>
-      <c r="C44" s="34" t="s">
+      <c r="C44" t="s">
         <v>272</v>
       </c>
       <c r="D44" t="s">
@@ -7110,8 +7103,8 @@
       <c r="H44" t="n">
         <v>0.0996</v>
       </c>
-      <c r="I44" t="e">
-        <v>#N/A</v>
+      <c r="I44" t="n">
+        <v>0.004</v>
       </c>
       <c r="J44" t="e">
         <v>#N/A</v>
@@ -7128,8 +7121,8 @@
       <c r="N44" t="n">
         <v>-22.5</v>
       </c>
-      <c r="O44" t="e">
-        <v>#N/A</v>
+      <c r="O44" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P44" t="e">
         <v>#N/A</v>
@@ -7141,7 +7134,7 @@
         <v>18.2</v>
       </c>
       <c r="S44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T44" t="e">
         <v>#N/A</v>
@@ -7158,29 +7151,29 @@
       <c r="X44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z44" t="e">
-        <v>#N/A</v>
+      <c r="Y44" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA44" t="s">
         <v>281</v>
       </c>
-      <c r="AB44" t="e">
-        <v>#N/A</v>
+      <c r="AB44" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF44" t="e">
-        <v>#N/A</v>
+      <c r="AD44" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG44" t="e">
         <v>#N/A</v>
@@ -7202,7 +7195,7 @@
       <c r="B45" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="34" t="s">
+      <c r="C45" t="s">
         <v>272</v>
       </c>
       <c r="D45" t="s">
@@ -7220,8 +7213,8 @@
       <c r="H45" t="n">
         <v>0.1009</v>
       </c>
-      <c r="I45" t="e">
-        <v>#N/A</v>
+      <c r="I45" t="n">
+        <v>0.004</v>
       </c>
       <c r="J45" t="e">
         <v>#N/A</v>
@@ -7238,8 +7231,8 @@
       <c r="N45" t="n">
         <v>-22.2</v>
       </c>
-      <c r="O45" t="e">
-        <v>#N/A</v>
+      <c r="O45" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P45" t="e">
         <v>#N/A</v>
@@ -7251,7 +7244,7 @@
         <v>18</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T45" t="e">
         <v>#N/A</v>
@@ -7268,29 +7261,29 @@
       <c r="X45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z45" t="e">
-        <v>#N/A</v>
+      <c r="Y45" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA45" t="s">
         <v>281</v>
       </c>
-      <c r="AB45" t="e">
-        <v>#N/A</v>
+      <c r="AB45" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF45" t="e">
-        <v>#N/A</v>
+      <c r="AD45" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG45" t="e">
         <v>#N/A</v>
@@ -7312,7 +7305,7 @@
       <c r="B46" t="s">
         <v>271</v>
       </c>
-      <c r="C46" s="34" t="s">
+      <c r="C46" t="s">
         <v>272</v>
       </c>
       <c r="D46" t="s">
@@ -7330,8 +7323,8 @@
       <c r="H46" t="n">
         <v>0.1022</v>
       </c>
-      <c r="I46" t="e">
-        <v>#N/A</v>
+      <c r="I46" t="n">
+        <v>0.004</v>
       </c>
       <c r="J46" t="e">
         <v>#N/A</v>
@@ -7348,8 +7341,8 @@
       <c r="N46" t="n">
         <v>-21.6</v>
       </c>
-      <c r="O46" t="e">
-        <v>#N/A</v>
+      <c r="O46" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P46" t="e">
         <v>#N/A</v>
@@ -7361,7 +7354,7 @@
         <v>18.8</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T46" t="e">
         <v>#N/A</v>
@@ -7378,29 +7371,29 @@
       <c r="X46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z46" t="e">
-        <v>#N/A</v>
+      <c r="Y46" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA46" t="s">
         <v>281</v>
       </c>
-      <c r="AB46" t="e">
-        <v>#N/A</v>
+      <c r="AB46" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF46" t="e">
-        <v>#N/A</v>
+      <c r="AD46" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG46" t="e">
         <v>#N/A</v>
@@ -7422,7 +7415,7 @@
       <c r="B47" t="s">
         <v>271</v>
       </c>
-      <c r="C47" s="34" t="s">
+      <c r="C47" t="s">
         <v>272</v>
       </c>
       <c r="D47" t="s">
@@ -7440,8 +7433,8 @@
       <c r="H47" t="n">
         <v>0.1035</v>
       </c>
-      <c r="I47" t="e">
-        <v>#N/A</v>
+      <c r="I47" t="n">
+        <v>0.004</v>
       </c>
       <c r="J47" t="e">
         <v>#N/A</v>
@@ -7458,8 +7451,8 @@
       <c r="N47" t="n">
         <v>-21.8</v>
       </c>
-      <c r="O47" t="e">
-        <v>#N/A</v>
+      <c r="O47" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P47" t="e">
         <v>#N/A</v>
@@ -7471,7 +7464,7 @@
         <v>18.3</v>
       </c>
       <c r="S47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T47" t="e">
         <v>#N/A</v>
@@ -7488,29 +7481,29 @@
       <c r="X47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z47" t="e">
-        <v>#N/A</v>
+      <c r="Y47" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA47" t="s">
         <v>281</v>
       </c>
-      <c r="AB47" t="e">
-        <v>#N/A</v>
+      <c r="AB47" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF47" t="e">
-        <v>#N/A</v>
+      <c r="AD47" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG47" t="e">
         <v>#N/A</v>
@@ -7532,7 +7525,7 @@
       <c r="B48" t="s">
         <v>271</v>
       </c>
-      <c r="C48" s="34" t="s">
+      <c r="C48" t="s">
         <v>272</v>
       </c>
       <c r="D48" t="s">
@@ -7550,8 +7543,8 @@
       <c r="H48" t="n">
         <v>0.1048</v>
       </c>
-      <c r="I48" t="e">
-        <v>#N/A</v>
+      <c r="I48" t="n">
+        <v>0.004</v>
       </c>
       <c r="J48" t="e">
         <v>#N/A</v>
@@ -7568,8 +7561,8 @@
       <c r="N48" t="n">
         <v>-22.3</v>
       </c>
-      <c r="O48" t="e">
-        <v>#N/A</v>
+      <c r="O48" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P48" t="e">
         <v>#N/A</v>
@@ -7581,7 +7574,7 @@
         <v>18.4</v>
       </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T48" t="e">
         <v>#N/A</v>
@@ -7598,29 +7591,29 @@
       <c r="X48" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z48" t="e">
-        <v>#N/A</v>
+      <c r="Y48" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA48" t="s">
         <v>281</v>
       </c>
-      <c r="AB48" t="e">
-        <v>#N/A</v>
+      <c r="AB48" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC48" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF48" t="e">
-        <v>#N/A</v>
+      <c r="AD48" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG48" t="e">
         <v>#N/A</v>
@@ -7642,7 +7635,7 @@
       <c r="B49" t="s">
         <v>271</v>
       </c>
-      <c r="C49" s="34" t="s">
+      <c r="C49" t="s">
         <v>272</v>
       </c>
       <c r="D49" t="s">
@@ -7660,8 +7653,8 @@
       <c r="H49" t="n">
         <v>0.1062</v>
       </c>
-      <c r="I49" t="e">
-        <v>#N/A</v>
+      <c r="I49" t="n">
+        <v>0.004</v>
       </c>
       <c r="J49" t="e">
         <v>#N/A</v>
@@ -7678,8 +7671,8 @@
       <c r="N49" t="n">
         <v>-21.8</v>
       </c>
-      <c r="O49" t="e">
-        <v>#N/A</v>
+      <c r="O49" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P49" t="e">
         <v>#N/A</v>
@@ -7691,7 +7684,7 @@
         <v>18.3</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T49" t="e">
         <v>#N/A</v>
@@ -7708,29 +7701,29 @@
       <c r="X49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z49" t="e">
-        <v>#N/A</v>
+      <c r="Y49" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA49" t="s">
         <v>281</v>
       </c>
-      <c r="AB49" t="e">
-        <v>#N/A</v>
+      <c r="AB49" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF49" t="e">
-        <v>#N/A</v>
+      <c r="AD49" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG49" t="e">
         <v>#N/A</v>
@@ -7752,7 +7745,7 @@
       <c r="B50" t="s">
         <v>271</v>
       </c>
-      <c r="C50" s="34" t="s">
+      <c r="C50" t="s">
         <v>272</v>
       </c>
       <c r="D50" t="s">
@@ -7770,8 +7763,8 @@
       <c r="H50" t="n">
         <v>0.1088</v>
       </c>
-      <c r="I50" t="e">
-        <v>#N/A</v>
+      <c r="I50" t="n">
+        <v>0.004</v>
       </c>
       <c r="J50" t="e">
         <v>#N/A</v>
@@ -7788,8 +7781,8 @@
       <c r="N50" t="n">
         <v>-21.6</v>
       </c>
-      <c r="O50" t="e">
-        <v>#N/A</v>
+      <c r="O50" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P50" t="e">
         <v>#N/A</v>
@@ -7801,7 +7794,7 @@
         <v>15.5</v>
       </c>
       <c r="S50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T50" t="e">
         <v>#N/A</v>
@@ -7818,29 +7811,29 @@
       <c r="X50" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z50" t="e">
-        <v>#N/A</v>
+      <c r="Y50" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA50" t="s">
         <v>281</v>
       </c>
-      <c r="AB50" t="e">
-        <v>#N/A</v>
+      <c r="AB50" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC50" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF50" t="e">
-        <v>#N/A</v>
+      <c r="AD50" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG50" t="e">
         <v>#N/A</v>
@@ -7862,7 +7855,7 @@
       <c r="B51" t="s">
         <v>271</v>
       </c>
-      <c r="C51" s="34" t="s">
+      <c r="C51" t="s">
         <v>272</v>
       </c>
       <c r="D51" t="s">
@@ -7880,8 +7873,8 @@
       <c r="H51" t="n">
         <v>0.1095</v>
       </c>
-      <c r="I51" t="e">
-        <v>#N/A</v>
+      <c r="I51" t="n">
+        <v>0.004</v>
       </c>
       <c r="J51" t="e">
         <v>#N/A</v>
@@ -7898,8 +7891,8 @@
       <c r="N51" t="n">
         <v>-21.9</v>
       </c>
-      <c r="O51" t="e">
-        <v>#N/A</v>
+      <c r="O51" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P51" t="e">
         <v>#N/A</v>
@@ -7911,7 +7904,7 @@
         <v>17.5</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T51" t="e">
         <v>#N/A</v>
@@ -7928,29 +7921,29 @@
       <c r="X51" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z51" t="e">
-        <v>#N/A</v>
+      <c r="Y51" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA51" t="s">
         <v>281</v>
       </c>
-      <c r="AB51" t="e">
-        <v>#N/A</v>
+      <c r="AB51" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC51" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF51" t="e">
-        <v>#N/A</v>
+      <c r="AD51" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG51" t="e">
         <v>#N/A</v>
@@ -7972,7 +7965,7 @@
       <c r="B52" t="s">
         <v>271</v>
       </c>
-      <c r="C52" s="34" t="s">
+      <c r="C52" t="s">
         <v>272</v>
       </c>
       <c r="D52" t="s">
@@ -7990,8 +7983,8 @@
       <c r="H52" t="n">
         <v>0.1101</v>
       </c>
-      <c r="I52" t="e">
-        <v>#N/A</v>
+      <c r="I52" t="n">
+        <v>0.004</v>
       </c>
       <c r="J52" t="e">
         <v>#N/A</v>
@@ -8008,8 +8001,8 @@
       <c r="N52" t="n">
         <v>-21.6</v>
       </c>
-      <c r="O52" t="e">
-        <v>#N/A</v>
+      <c r="O52" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P52" t="e">
         <v>#N/A</v>
@@ -8021,7 +8014,7 @@
         <v>16.5</v>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T52" t="e">
         <v>#N/A</v>
@@ -8038,29 +8031,29 @@
       <c r="X52" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z52" t="e">
-        <v>#N/A</v>
+      <c r="Y52" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA52" t="s">
         <v>281</v>
       </c>
-      <c r="AB52" t="e">
-        <v>#N/A</v>
+      <c r="AB52" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC52" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF52" t="e">
-        <v>#N/A</v>
+      <c r="AD52" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG52" t="e">
         <v>#N/A</v>
@@ -8082,7 +8075,7 @@
       <c r="B53" t="s">
         <v>271</v>
       </c>
-      <c r="C53" s="34" t="s">
+      <c r="C53" t="s">
         <v>272</v>
       </c>
       <c r="D53" t="s">
@@ -8100,8 +8093,8 @@
       <c r="H53" t="n">
         <v>0.1107</v>
       </c>
-      <c r="I53" t="e">
-        <v>#N/A</v>
+      <c r="I53" t="n">
+        <v>0.004</v>
       </c>
       <c r="J53" t="e">
         <v>#N/A</v>
@@ -8118,8 +8111,8 @@
       <c r="N53" t="n">
         <v>-21.8</v>
       </c>
-      <c r="O53" t="e">
-        <v>#N/A</v>
+      <c r="O53" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P53" t="e">
         <v>#N/A</v>
@@ -8131,7 +8124,7 @@
         <v>15.4</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T53" t="e">
         <v>#N/A</v>
@@ -8148,29 +8141,29 @@
       <c r="X53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z53" t="e">
-        <v>#N/A</v>
+      <c r="Y53" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA53" t="s">
         <v>281</v>
       </c>
-      <c r="AB53" t="e">
-        <v>#N/A</v>
+      <c r="AB53" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF53" t="e">
-        <v>#N/A</v>
+      <c r="AD53" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG53" t="e">
         <v>#N/A</v>
@@ -8192,7 +8185,7 @@
       <c r="B54" t="s">
         <v>271</v>
       </c>
-      <c r="C54" s="34" t="s">
+      <c r="C54" t="s">
         <v>272</v>
       </c>
       <c r="D54" t="s">
@@ -8210,8 +8203,8 @@
       <c r="H54" t="n">
         <v>0.1125</v>
       </c>
-      <c r="I54" t="e">
-        <v>#N/A</v>
+      <c r="I54" t="n">
+        <v>0.004</v>
       </c>
       <c r="J54" t="e">
         <v>#N/A</v>
@@ -8228,8 +8221,8 @@
       <c r="N54" t="n">
         <v>-22.3</v>
       </c>
-      <c r="O54" t="e">
-        <v>#N/A</v>
+      <c r="O54" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P54" t="e">
         <v>#N/A</v>
@@ -8241,7 +8234,7 @@
         <v>15.9</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T54" t="e">
         <v>#N/A</v>
@@ -8258,29 +8251,29 @@
       <c r="X54" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z54" t="e">
-        <v>#N/A</v>
+      <c r="Y54" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA54" t="s">
         <v>281</v>
       </c>
-      <c r="AB54" t="e">
-        <v>#N/A</v>
+      <c r="AB54" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC54" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF54" t="e">
-        <v>#N/A</v>
+      <c r="AD54" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG54" t="e">
         <v>#N/A</v>
@@ -8302,7 +8295,7 @@
       <c r="B55" t="s">
         <v>271</v>
       </c>
-      <c r="C55" s="34" t="s">
+      <c r="C55" t="s">
         <v>272</v>
       </c>
       <c r="D55" t="s">
@@ -8320,8 +8313,8 @@
       <c r="H55" t="n">
         <v>0.1131</v>
       </c>
-      <c r="I55" t="e">
-        <v>#N/A</v>
+      <c r="I55" t="n">
+        <v>0.004</v>
       </c>
       <c r="J55" t="e">
         <v>#N/A</v>
@@ -8338,8 +8331,8 @@
       <c r="N55" t="n">
         <v>-22.5</v>
       </c>
-      <c r="O55" t="e">
-        <v>#N/A</v>
+      <c r="O55" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P55" t="e">
         <v>#N/A</v>
@@ -8351,7 +8344,7 @@
         <v>14.6</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T55" t="e">
         <v>#N/A</v>
@@ -8368,29 +8361,29 @@
       <c r="X55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z55" t="e">
-        <v>#N/A</v>
+      <c r="Y55" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA55" t="s">
         <v>281</v>
       </c>
-      <c r="AB55" t="e">
-        <v>#N/A</v>
+      <c r="AB55" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF55" t="e">
-        <v>#N/A</v>
+      <c r="AD55" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG55" t="e">
         <v>#N/A</v>
@@ -8412,7 +8405,7 @@
       <c r="B56" t="s">
         <v>271</v>
       </c>
-      <c r="C56" s="34" t="s">
+      <c r="C56" t="s">
         <v>272</v>
       </c>
       <c r="D56" t="s">
@@ -8430,8 +8423,8 @@
       <c r="H56" t="n">
         <v>0.1137</v>
       </c>
-      <c r="I56" t="e">
-        <v>#N/A</v>
+      <c r="I56" t="n">
+        <v>0.004</v>
       </c>
       <c r="J56" t="e">
         <v>#N/A</v>
@@ -8448,8 +8441,8 @@
       <c r="N56" t="n">
         <v>-22.4</v>
       </c>
-      <c r="O56" t="e">
-        <v>#N/A</v>
+      <c r="O56" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P56" t="e">
         <v>#N/A</v>
@@ -8461,7 +8454,7 @@
         <v>14.4</v>
       </c>
       <c r="S56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T56" t="e">
         <v>#N/A</v>
@@ -8478,29 +8471,29 @@
       <c r="X56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z56" t="e">
-        <v>#N/A</v>
+      <c r="Y56" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA56" t="s">
         <v>281</v>
       </c>
-      <c r="AB56" t="e">
-        <v>#N/A</v>
+      <c r="AB56" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF56" t="e">
-        <v>#N/A</v>
+      <c r="AD56" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG56" t="e">
         <v>#N/A</v>
@@ -8522,7 +8515,7 @@
       <c r="B57" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="34" t="s">
+      <c r="C57" t="s">
         <v>272</v>
       </c>
       <c r="D57" t="s">
@@ -8540,8 +8533,8 @@
       <c r="H57" t="n">
         <v>0.1143</v>
       </c>
-      <c r="I57" t="e">
-        <v>#N/A</v>
+      <c r="I57" t="n">
+        <v>0.004</v>
       </c>
       <c r="J57" t="e">
         <v>#N/A</v>
@@ -8558,8 +8551,8 @@
       <c r="N57" t="n">
         <v>-22.7</v>
       </c>
-      <c r="O57" t="e">
-        <v>#N/A</v>
+      <c r="O57" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P57" t="e">
         <v>#N/A</v>
@@ -8571,7 +8564,7 @@
         <v>16.4</v>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T57" t="e">
         <v>#N/A</v>
@@ -8588,29 +8581,29 @@
       <c r="X57" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z57" t="e">
-        <v>#N/A</v>
+      <c r="Y57" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA57" t="s">
         <v>281</v>
       </c>
-      <c r="AB57" t="e">
-        <v>#N/A</v>
+      <c r="AB57" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC57" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF57" t="e">
-        <v>#N/A</v>
+      <c r="AD57" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG57" t="e">
         <v>#N/A</v>
@@ -8632,7 +8625,7 @@
       <c r="B58" t="s">
         <v>271</v>
       </c>
-      <c r="C58" s="34" t="s">
+      <c r="C58" t="s">
         <v>272</v>
       </c>
       <c r="D58" t="s">
@@ -8650,8 +8643,8 @@
       <c r="H58" t="n">
         <v>0.1149</v>
       </c>
-      <c r="I58" t="e">
-        <v>#N/A</v>
+      <c r="I58" t="n">
+        <v>0.004</v>
       </c>
       <c r="J58" t="e">
         <v>#N/A</v>
@@ -8668,8 +8661,8 @@
       <c r="N58" t="n">
         <v>-21.8</v>
       </c>
-      <c r="O58" t="e">
-        <v>#N/A</v>
+      <c r="O58" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P58" t="e">
         <v>#N/A</v>
@@ -8681,7 +8674,7 @@
         <v>16.9</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T58" t="e">
         <v>#N/A</v>
@@ -8698,29 +8691,29 @@
       <c r="X58" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z58" t="e">
-        <v>#N/A</v>
+      <c r="Y58" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA58" t="s">
         <v>281</v>
       </c>
-      <c r="AB58" t="e">
-        <v>#N/A</v>
+      <c r="AB58" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC58" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF58" t="e">
-        <v>#N/A</v>
+      <c r="AD58" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG58" t="e">
         <v>#N/A</v>
@@ -8742,7 +8735,7 @@
       <c r="B59" t="s">
         <v>271</v>
       </c>
-      <c r="C59" s="34" t="s">
+      <c r="C59" t="s">
         <v>272</v>
       </c>
       <c r="D59" t="s">
@@ -8760,8 +8753,8 @@
       <c r="H59" t="n">
         <v>0.1155</v>
       </c>
-      <c r="I59" t="e">
-        <v>#N/A</v>
+      <c r="I59" t="n">
+        <v>0.004</v>
       </c>
       <c r="J59" t="e">
         <v>#N/A</v>
@@ -8778,8 +8771,8 @@
       <c r="N59" t="n">
         <v>-22.9</v>
       </c>
-      <c r="O59" t="e">
-        <v>#N/A</v>
+      <c r="O59" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P59" t="e">
         <v>#N/A</v>
@@ -8791,7 +8784,7 @@
         <v>14.2</v>
       </c>
       <c r="S59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T59" t="e">
         <v>#N/A</v>
@@ -8808,29 +8801,29 @@
       <c r="X59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z59" t="e">
-        <v>#N/A</v>
+      <c r="Y59" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA59" t="s">
         <v>281</v>
       </c>
-      <c r="AB59" t="e">
-        <v>#N/A</v>
+      <c r="AB59" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF59" t="e">
-        <v>#N/A</v>
+      <c r="AD59" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG59" t="e">
         <v>#N/A</v>
@@ -8852,7 +8845,7 @@
       <c r="B60" t="s">
         <v>271</v>
       </c>
-      <c r="C60" s="34" t="s">
+      <c r="C60" t="s">
         <v>272</v>
       </c>
       <c r="D60" t="s">
@@ -8870,8 +8863,8 @@
       <c r="H60" t="n">
         <v>0.1161</v>
       </c>
-      <c r="I60" t="e">
-        <v>#N/A</v>
+      <c r="I60" t="n">
+        <v>0.004</v>
       </c>
       <c r="J60" t="e">
         <v>#N/A</v>
@@ -8888,8 +8881,8 @@
       <c r="N60" t="n">
         <v>-22.1</v>
       </c>
-      <c r="O60" t="e">
-        <v>#N/A</v>
+      <c r="O60" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P60" t="e">
         <v>#N/A</v>
@@ -8901,7 +8894,7 @@
         <v>17</v>
       </c>
       <c r="S60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T60" t="e">
         <v>#N/A</v>
@@ -8918,29 +8911,29 @@
       <c r="X60" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z60" t="e">
-        <v>#N/A</v>
+      <c r="Y60" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA60" t="s">
         <v>281</v>
       </c>
-      <c r="AB60" t="e">
-        <v>#N/A</v>
+      <c r="AB60" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC60" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF60" t="e">
-        <v>#N/A</v>
+      <c r="AD60" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG60" t="e">
         <v>#N/A</v>
@@ -8962,7 +8955,7 @@
       <c r="B61" t="s">
         <v>271</v>
       </c>
-      <c r="C61" s="34" t="s">
+      <c r="C61" t="s">
         <v>272</v>
       </c>
       <c r="D61" t="s">
@@ -8980,8 +8973,8 @@
       <c r="H61" t="n">
         <v>0.1165</v>
       </c>
-      <c r="I61" t="e">
-        <v>#N/A</v>
+      <c r="I61" t="n">
+        <v>0.004</v>
       </c>
       <c r="J61" t="e">
         <v>#N/A</v>
@@ -8998,8 +8991,8 @@
       <c r="N61" t="n">
         <v>-23</v>
       </c>
-      <c r="O61" t="e">
-        <v>#N/A</v>
+      <c r="O61" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P61" t="e">
         <v>#N/A</v>
@@ -9011,7 +9004,7 @@
         <v>20.3</v>
       </c>
       <c r="S61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T61" t="e">
         <v>#N/A</v>
@@ -9028,29 +9021,29 @@
       <c r="X61" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z61" t="e">
-        <v>#N/A</v>
+      <c r="Y61" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA61" t="s">
         <v>281</v>
       </c>
-      <c r="AB61" t="e">
-        <v>#N/A</v>
+      <c r="AB61" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC61" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF61" t="e">
-        <v>#N/A</v>
+      <c r="AD61" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG61" t="e">
         <v>#N/A</v>
@@ -9072,7 +9065,7 @@
       <c r="B62" t="s">
         <v>271</v>
       </c>
-      <c r="C62" s="34" t="s">
+      <c r="C62" t="s">
         <v>272</v>
       </c>
       <c r="D62" t="s">
@@ -9090,8 +9083,8 @@
       <c r="H62" t="n">
         <v>0.1174</v>
       </c>
-      <c r="I62" t="e">
-        <v>#N/A</v>
+      <c r="I62" t="n">
+        <v>0.004</v>
       </c>
       <c r="J62" t="e">
         <v>#N/A</v>
@@ -9108,8 +9101,8 @@
       <c r="N62" t="n">
         <v>-21.2</v>
       </c>
-      <c r="O62" t="e">
-        <v>#N/A</v>
+      <c r="O62" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P62" t="e">
         <v>#N/A</v>
@@ -9121,7 +9114,7 @@
         <v>18</v>
       </c>
       <c r="S62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T62" t="e">
         <v>#N/A</v>
@@ -9138,29 +9131,29 @@
       <c r="X62" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z62" t="e">
-        <v>#N/A</v>
+      <c r="Y62" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA62" t="s">
         <v>281</v>
       </c>
-      <c r="AB62" t="e">
-        <v>#N/A</v>
+      <c r="AB62" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC62" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF62" t="e">
-        <v>#N/A</v>
+      <c r="AD62" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG62" t="e">
         <v>#N/A</v>
@@ -9182,7 +9175,7 @@
       <c r="B63" t="s">
         <v>271</v>
       </c>
-      <c r="C63" s="34" t="s">
+      <c r="C63" t="s">
         <v>272</v>
       </c>
       <c r="D63" t="s">
@@ -9200,8 +9193,8 @@
       <c r="H63" t="n">
         <v>0.1183</v>
       </c>
-      <c r="I63" t="e">
-        <v>#N/A</v>
+      <c r="I63" t="n">
+        <v>0.004</v>
       </c>
       <c r="J63" t="e">
         <v>#N/A</v>
@@ -9218,8 +9211,8 @@
       <c r="N63" t="n">
         <v>-22.1</v>
       </c>
-      <c r="O63" t="e">
-        <v>#N/A</v>
+      <c r="O63" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P63" t="e">
         <v>#N/A</v>
@@ -9231,7 +9224,7 @@
         <v>17.5</v>
       </c>
       <c r="S63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T63" t="e">
         <v>#N/A</v>
@@ -9248,29 +9241,29 @@
       <c r="X63" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z63" t="e">
-        <v>#N/A</v>
+      <c r="Y63" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA63" t="s">
         <v>281</v>
       </c>
-      <c r="AB63" t="e">
-        <v>#N/A</v>
+      <c r="AB63" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC63" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF63" t="e">
-        <v>#N/A</v>
+      <c r="AD63" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG63" t="e">
         <v>#N/A</v>
@@ -9292,7 +9285,7 @@
       <c r="B64" t="s">
         <v>271</v>
       </c>
-      <c r="C64" s="34" t="s">
+      <c r="C64" t="s">
         <v>272</v>
       </c>
       <c r="D64" t="s">
@@ -9310,8 +9303,8 @@
       <c r="H64" t="n">
         <v>0.1191</v>
       </c>
-      <c r="I64" t="e">
-        <v>#N/A</v>
+      <c r="I64" t="n">
+        <v>0.004</v>
       </c>
       <c r="J64" t="e">
         <v>#N/A</v>
@@ -9328,8 +9321,8 @@
       <c r="N64" t="n">
         <v>-21.7</v>
       </c>
-      <c r="O64" t="e">
-        <v>#N/A</v>
+      <c r="O64" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P64" t="e">
         <v>#N/A</v>
@@ -9341,7 +9334,7 @@
         <v>19.5</v>
       </c>
       <c r="S64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T64" t="e">
         <v>#N/A</v>
@@ -9358,29 +9351,29 @@
       <c r="X64" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z64" t="e">
-        <v>#N/A</v>
+      <c r="Y64" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA64" t="s">
         <v>281</v>
       </c>
-      <c r="AB64" t="e">
-        <v>#N/A</v>
+      <c r="AB64" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC64" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF64" t="e">
-        <v>#N/A</v>
+      <c r="AD64" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG64" t="e">
         <v>#N/A</v>
@@ -9402,7 +9395,7 @@
       <c r="B65" t="s">
         <v>271</v>
       </c>
-      <c r="C65" s="34" t="s">
+      <c r="C65" t="s">
         <v>272</v>
       </c>
       <c r="D65" t="s">
@@ -9420,8 +9413,8 @@
       <c r="H65" t="n">
         <v>0.12</v>
       </c>
-      <c r="I65" t="e">
-        <v>#N/A</v>
+      <c r="I65" t="n">
+        <v>0.004</v>
       </c>
       <c r="J65" t="e">
         <v>#N/A</v>
@@ -9438,8 +9431,8 @@
       <c r="N65" t="n">
         <v>-21.7</v>
       </c>
-      <c r="O65" t="e">
-        <v>#N/A</v>
+      <c r="O65" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P65" t="e">
         <v>#N/A</v>
@@ -9451,7 +9444,7 @@
         <v>19.1</v>
       </c>
       <c r="S65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T65" t="e">
         <v>#N/A</v>
@@ -9468,29 +9461,29 @@
       <c r="X65" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z65" t="e">
-        <v>#N/A</v>
+      <c r="Y65" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA65" t="s">
         <v>281</v>
       </c>
-      <c r="AB65" t="e">
-        <v>#N/A</v>
+      <c r="AB65" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC65" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF65" t="e">
-        <v>#N/A</v>
+      <c r="AD65" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG65" t="e">
         <v>#N/A</v>
@@ -9512,7 +9505,7 @@
       <c r="B66" t="s">
         <v>271</v>
       </c>
-      <c r="C66" s="34" t="s">
+      <c r="C66" t="s">
         <v>272</v>
       </c>
       <c r="D66" t="s">
@@ -9530,8 +9523,8 @@
       <c r="H66" t="n">
         <v>0.1209</v>
       </c>
-      <c r="I66" t="e">
-        <v>#N/A</v>
+      <c r="I66" t="n">
+        <v>0.004</v>
       </c>
       <c r="J66" t="e">
         <v>#N/A</v>
@@ -9548,8 +9541,8 @@
       <c r="N66" t="n">
         <v>-21.3</v>
       </c>
-      <c r="O66" t="e">
-        <v>#N/A</v>
+      <c r="O66" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P66" t="e">
         <v>#N/A</v>
@@ -9561,7 +9554,7 @@
         <v>19.7</v>
       </c>
       <c r="S66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T66" t="e">
         <v>#N/A</v>
@@ -9578,29 +9571,29 @@
       <c r="X66" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z66" t="e">
-        <v>#N/A</v>
+      <c r="Y66" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA66" t="s">
         <v>281</v>
       </c>
-      <c r="AB66" t="e">
-        <v>#N/A</v>
+      <c r="AB66" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC66" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF66" t="e">
-        <v>#N/A</v>
+      <c r="AD66" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG66" t="e">
         <v>#N/A</v>
@@ -9622,7 +9615,7 @@
       <c r="B67" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="34" t="s">
+      <c r="C67" t="s">
         <v>272</v>
       </c>
       <c r="D67" t="s">
@@ -9640,8 +9633,8 @@
       <c r="H67" t="n">
         <v>0.1218</v>
       </c>
-      <c r="I67" t="e">
-        <v>#N/A</v>
+      <c r="I67" t="n">
+        <v>0.004</v>
       </c>
       <c r="J67" t="e">
         <v>#N/A</v>
@@ -9658,8 +9651,8 @@
       <c r="N67" t="n">
         <v>-22</v>
       </c>
-      <c r="O67" t="e">
-        <v>#N/A</v>
+      <c r="O67" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P67" t="e">
         <v>#N/A</v>
@@ -9671,7 +9664,7 @@
         <v>19.4</v>
       </c>
       <c r="S67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T67" t="e">
         <v>#N/A</v>
@@ -9688,29 +9681,29 @@
       <c r="X67" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z67" t="e">
-        <v>#N/A</v>
+      <c r="Y67" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA67" t="s">
         <v>281</v>
       </c>
-      <c r="AB67" t="e">
-        <v>#N/A</v>
+      <c r="AB67" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC67" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF67" t="e">
-        <v>#N/A</v>
+      <c r="AD67" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG67" t="e">
         <v>#N/A</v>
@@ -9732,7 +9725,7 @@
       <c r="B68" t="s">
         <v>271</v>
       </c>
-      <c r="C68" s="34" t="s">
+      <c r="C68" t="s">
         <v>272</v>
       </c>
       <c r="D68" t="s">
@@ -9750,8 +9743,8 @@
       <c r="H68" t="n">
         <v>0.1227</v>
       </c>
-      <c r="I68" t="e">
-        <v>#N/A</v>
+      <c r="I68" t="n">
+        <v>0.004</v>
       </c>
       <c r="J68" t="e">
         <v>#N/A</v>
@@ -9768,8 +9761,8 @@
       <c r="N68" t="n">
         <v>-22.3</v>
       </c>
-      <c r="O68" t="e">
-        <v>#N/A</v>
+      <c r="O68" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P68" t="e">
         <v>#N/A</v>
@@ -9781,7 +9774,7 @@
         <v>19.8</v>
       </c>
       <c r="S68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T68" t="e">
         <v>#N/A</v>
@@ -9798,29 +9791,29 @@
       <c r="X68" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z68" t="e">
-        <v>#N/A</v>
+      <c r="Y68" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA68" t="s">
         <v>281</v>
       </c>
-      <c r="AB68" t="e">
-        <v>#N/A</v>
+      <c r="AB68" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC68" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF68" t="e">
-        <v>#N/A</v>
+      <c r="AD68" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG68" t="e">
         <v>#N/A</v>
@@ -9842,7 +9835,7 @@
       <c r="B69" t="s">
         <v>271</v>
       </c>
-      <c r="C69" s="34" t="s">
+      <c r="C69" t="s">
         <v>272</v>
       </c>
       <c r="D69" t="s">
@@ -9860,8 +9853,8 @@
       <c r="H69" t="n">
         <v>0.1235</v>
       </c>
-      <c r="I69" t="e">
-        <v>#N/A</v>
+      <c r="I69" t="n">
+        <v>0.004</v>
       </c>
       <c r="J69" t="e">
         <v>#N/A</v>
@@ -9878,8 +9871,8 @@
       <c r="N69" t="n">
         <v>-22</v>
       </c>
-      <c r="O69" t="e">
-        <v>#N/A</v>
+      <c r="O69" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P69" t="e">
         <v>#N/A</v>
@@ -9891,7 +9884,7 @@
         <v>19.6</v>
       </c>
       <c r="S69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T69" t="e">
         <v>#N/A</v>
@@ -9908,29 +9901,29 @@
       <c r="X69" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z69" t="e">
-        <v>#N/A</v>
+      <c r="Y69" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA69" t="s">
         <v>281</v>
       </c>
-      <c r="AB69" t="e">
-        <v>#N/A</v>
+      <c r="AB69" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC69" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF69" t="e">
-        <v>#N/A</v>
+      <c r="AD69" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG69" t="e">
         <v>#N/A</v>
@@ -9952,7 +9945,7 @@
       <c r="B70" t="s">
         <v>271</v>
       </c>
-      <c r="C70" s="34" t="s">
+      <c r="C70" t="s">
         <v>272</v>
       </c>
       <c r="D70" t="s">
@@ -9970,8 +9963,8 @@
       <c r="H70" t="n">
         <v>0.1244</v>
       </c>
-      <c r="I70" t="e">
-        <v>#N/A</v>
+      <c r="I70" t="n">
+        <v>0.004</v>
       </c>
       <c r="J70" t="e">
         <v>#N/A</v>
@@ -9988,8 +9981,8 @@
       <c r="N70" t="n">
         <v>-22.4</v>
       </c>
-      <c r="O70" t="e">
-        <v>#N/A</v>
+      <c r="O70" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P70" t="e">
         <v>#N/A</v>
@@ -10001,7 +9994,7 @@
         <v>19.5</v>
       </c>
       <c r="S70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T70" t="e">
         <v>#N/A</v>
@@ -10018,29 +10011,29 @@
       <c r="X70" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z70" t="e">
-        <v>#N/A</v>
+      <c r="Y70" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA70" t="s">
         <v>281</v>
       </c>
-      <c r="AB70" t="e">
-        <v>#N/A</v>
+      <c r="AB70" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC70" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF70" t="e">
-        <v>#N/A</v>
+      <c r="AD70" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG70" t="e">
         <v>#N/A</v>
@@ -10062,7 +10055,7 @@
       <c r="B71" t="s">
         <v>271</v>
       </c>
-      <c r="C71" s="34" t="s">
+      <c r="C71" t="s">
         <v>272</v>
       </c>
       <c r="D71" t="s">
@@ -10080,8 +10073,8 @@
       <c r="H71" t="n">
         <v>0.1253</v>
       </c>
-      <c r="I71" t="e">
-        <v>#N/A</v>
+      <c r="I71" t="n">
+        <v>0.004</v>
       </c>
       <c r="J71" t="e">
         <v>#N/A</v>
@@ -10098,8 +10091,8 @@
       <c r="N71" t="n">
         <v>-22.4</v>
       </c>
-      <c r="O71" t="e">
-        <v>#N/A</v>
+      <c r="O71" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P71" t="e">
         <v>#N/A</v>
@@ -10111,7 +10104,7 @@
         <v>19.5</v>
       </c>
       <c r="S71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T71" t="e">
         <v>#N/A</v>
@@ -10128,29 +10121,29 @@
       <c r="X71" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z71" t="e">
-        <v>#N/A</v>
+      <c r="Y71" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA71" t="s">
         <v>281</v>
       </c>
-      <c r="AB71" t="e">
-        <v>#N/A</v>
+      <c r="AB71" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC71" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF71" t="e">
-        <v>#N/A</v>
+      <c r="AD71" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG71" t="e">
         <v>#N/A</v>
@@ -10172,7 +10165,7 @@
       <c r="B72" t="s">
         <v>271</v>
       </c>
-      <c r="C72" s="34" t="s">
+      <c r="C72" t="s">
         <v>272</v>
       </c>
       <c r="D72" t="s">
@@ -10190,8 +10183,8 @@
       <c r="H72" t="n">
         <v>0.1262</v>
       </c>
-      <c r="I72" t="e">
-        <v>#N/A</v>
+      <c r="I72" t="n">
+        <v>0.004</v>
       </c>
       <c r="J72" t="e">
         <v>#N/A</v>
@@ -10208,8 +10201,8 @@
       <c r="N72" t="n">
         <v>-22</v>
       </c>
-      <c r="O72" t="e">
-        <v>#N/A</v>
+      <c r="O72" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P72" t="e">
         <v>#N/A</v>
@@ -10221,7 +10214,7 @@
         <v>19.6</v>
       </c>
       <c r="S72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T72" t="e">
         <v>#N/A</v>
@@ -10238,29 +10231,29 @@
       <c r="X72" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z72" t="e">
-        <v>#N/A</v>
+      <c r="Y72" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA72" t="s">
         <v>281</v>
       </c>
-      <c r="AB72" t="e">
-        <v>#N/A</v>
+      <c r="AB72" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC72" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF72" t="e">
-        <v>#N/A</v>
+      <c r="AD72" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG72" t="e">
         <v>#N/A</v>
@@ -10282,7 +10275,7 @@
       <c r="B73" t="s">
         <v>271</v>
       </c>
-      <c r="C73" s="34" t="s">
+      <c r="C73" t="s">
         <v>272</v>
       </c>
       <c r="D73" t="s">
@@ -10300,8 +10293,8 @@
       <c r="H73" t="n">
         <v>0.1271</v>
       </c>
-      <c r="I73" t="e">
-        <v>#N/A</v>
+      <c r="I73" t="n">
+        <v>0.004</v>
       </c>
       <c r="J73" t="e">
         <v>#N/A</v>
@@ -10318,8 +10311,8 @@
       <c r="N73" t="n">
         <v>-22.1</v>
       </c>
-      <c r="O73" t="e">
-        <v>#N/A</v>
+      <c r="O73" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P73" t="e">
         <v>#N/A</v>
@@ -10331,7 +10324,7 @@
         <v>20</v>
       </c>
       <c r="S73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T73" t="e">
         <v>#N/A</v>
@@ -10348,29 +10341,29 @@
       <c r="X73" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z73" t="e">
-        <v>#N/A</v>
+      <c r="Y73" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA73" t="s">
         <v>281</v>
       </c>
-      <c r="AB73" t="e">
-        <v>#N/A</v>
+      <c r="AB73" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC73" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF73" t="e">
-        <v>#N/A</v>
+      <c r="AD73" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG73" t="e">
         <v>#N/A</v>
@@ -10392,7 +10385,7 @@
       <c r="B74" t="s">
         <v>271</v>
       </c>
-      <c r="C74" s="34" t="s">
+      <c r="C74" t="s">
         <v>272</v>
       </c>
       <c r="D74" t="s">
@@ -10410,8 +10403,8 @@
       <c r="H74" t="n">
         <v>0.1279</v>
       </c>
-      <c r="I74" t="e">
-        <v>#N/A</v>
+      <c r="I74" t="n">
+        <v>0.004</v>
       </c>
       <c r="J74" t="e">
         <v>#N/A</v>
@@ -10428,8 +10421,8 @@
       <c r="N74" t="n">
         <v>-22.1</v>
       </c>
-      <c r="O74" t="e">
-        <v>#N/A</v>
+      <c r="O74" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P74" t="e">
         <v>#N/A</v>
@@ -10441,7 +10434,7 @@
         <v>20.4</v>
       </c>
       <c r="S74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T74" t="e">
         <v>#N/A</v>
@@ -10458,29 +10451,29 @@
       <c r="X74" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z74" t="e">
-        <v>#N/A</v>
+      <c r="Y74" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA74" t="s">
         <v>281</v>
       </c>
-      <c r="AB74" t="e">
-        <v>#N/A</v>
+      <c r="AB74" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC74" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF74" t="e">
-        <v>#N/A</v>
+      <c r="AD74" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG74" t="e">
         <v>#N/A</v>
@@ -10502,7 +10495,7 @@
       <c r="B75" t="s">
         <v>271</v>
       </c>
-      <c r="C75" s="34" t="s">
+      <c r="C75" t="s">
         <v>272</v>
       </c>
       <c r="D75" t="s">
@@ -10520,8 +10513,8 @@
       <c r="H75" t="n">
         <v>0.1288</v>
       </c>
-      <c r="I75" t="e">
-        <v>#N/A</v>
+      <c r="I75" t="n">
+        <v>0.004</v>
       </c>
       <c r="J75" t="e">
         <v>#N/A</v>
@@ -10538,8 +10531,8 @@
       <c r="N75" t="n">
         <v>-22.3</v>
       </c>
-      <c r="O75" t="e">
-        <v>#N/A</v>
+      <c r="O75" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P75" t="e">
         <v>#N/A</v>
@@ -10551,7 +10544,7 @@
         <v>20.7</v>
       </c>
       <c r="S75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T75" t="e">
         <v>#N/A</v>
@@ -10568,29 +10561,29 @@
       <c r="X75" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z75" t="e">
-        <v>#N/A</v>
+      <c r="Y75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA75" t="s">
         <v>281</v>
       </c>
-      <c r="AB75" t="e">
-        <v>#N/A</v>
+      <c r="AB75" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC75" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF75" t="e">
-        <v>#N/A</v>
+      <c r="AD75" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG75" t="e">
         <v>#N/A</v>
@@ -10612,7 +10605,7 @@
       <c r="B76" t="s">
         <v>271</v>
       </c>
-      <c r="C76" s="34" t="s">
+      <c r="C76" t="s">
         <v>272</v>
       </c>
       <c r="D76" t="s">
@@ -10630,8 +10623,8 @@
       <c r="H76" t="n">
         <v>0.1304</v>
       </c>
-      <c r="I76" t="e">
-        <v>#N/A</v>
+      <c r="I76" t="n">
+        <v>0.004</v>
       </c>
       <c r="J76" t="e">
         <v>#N/A</v>
@@ -10648,8 +10641,8 @@
       <c r="N76" t="n">
         <v>-22.5</v>
       </c>
-      <c r="O76" t="e">
-        <v>#N/A</v>
+      <c r="O76" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P76" t="e">
         <v>#N/A</v>
@@ -10661,7 +10654,7 @@
         <v>21.3</v>
       </c>
       <c r="S76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T76" t="e">
         <v>#N/A</v>
@@ -10678,29 +10671,29 @@
       <c r="X76" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z76" t="e">
-        <v>#N/A</v>
+      <c r="Y76" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA76" t="s">
         <v>281</v>
       </c>
-      <c r="AB76" t="e">
-        <v>#N/A</v>
+      <c r="AB76" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC76" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF76" t="e">
-        <v>#N/A</v>
+      <c r="AD76" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG76" t="e">
         <v>#N/A</v>
@@ -10722,7 +10715,7 @@
       <c r="B77" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="34" t="s">
+      <c r="C77" t="s">
         <v>272</v>
       </c>
       <c r="D77" t="s">
@@ -10740,8 +10733,8 @@
       <c r="H77" t="n">
         <v>0.1335</v>
       </c>
-      <c r="I77" t="e">
-        <v>#N/A</v>
+      <c r="I77" t="n">
+        <v>0.004</v>
       </c>
       <c r="J77" t="e">
         <v>#N/A</v>
@@ -10758,8 +10751,8 @@
       <c r="N77" t="n">
         <v>-24.3</v>
       </c>
-      <c r="O77" t="e">
-        <v>#N/A</v>
+      <c r="O77" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P77" t="e">
         <v>#N/A</v>
@@ -10771,7 +10764,7 @@
         <v>8.1</v>
       </c>
       <c r="S77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T77" t="e">
         <v>#N/A</v>
@@ -10788,29 +10781,29 @@
       <c r="X77" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z77" t="e">
-        <v>#N/A</v>
+      <c r="Y77" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA77" t="s">
         <v>281</v>
       </c>
-      <c r="AB77" t="e">
-        <v>#N/A</v>
+      <c r="AB77" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC77" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF77" t="e">
-        <v>#N/A</v>
+      <c r="AD77" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG77" t="e">
         <v>#N/A</v>
@@ -10832,7 +10825,7 @@
       <c r="B78" t="s">
         <v>271</v>
       </c>
-      <c r="C78" s="34" t="s">
+      <c r="C78" t="s">
         <v>272</v>
       </c>
       <c r="D78" t="s">
@@ -10850,8 +10843,8 @@
       <c r="H78" t="n">
         <v>0.1384</v>
       </c>
-      <c r="I78" t="e">
-        <v>#N/A</v>
+      <c r="I78" t="n">
+        <v>0.004</v>
       </c>
       <c r="J78" t="e">
         <v>#N/A</v>
@@ -10868,8 +10861,8 @@
       <c r="N78" t="n">
         <v>-24.3</v>
       </c>
-      <c r="O78" t="e">
-        <v>#N/A</v>
+      <c r="O78" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P78" t="e">
         <v>#N/A</v>
@@ -10881,7 +10874,7 @@
         <v>7.4</v>
       </c>
       <c r="S78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T78" t="e">
         <v>#N/A</v>
@@ -10898,29 +10891,29 @@
       <c r="X78" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z78" t="e">
-        <v>#N/A</v>
+      <c r="Y78" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA78" t="s">
         <v>281</v>
       </c>
-      <c r="AB78" t="e">
-        <v>#N/A</v>
+      <c r="AB78" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC78" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF78" t="e">
-        <v>#N/A</v>
+      <c r="AD78" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG78" t="e">
         <v>#N/A</v>
@@ -10942,7 +10935,7 @@
       <c r="B79" t="s">
         <v>271</v>
       </c>
-      <c r="C79" s="34" t="s">
+      <c r="C79" t="s">
         <v>272</v>
       </c>
       <c r="D79" t="s">
@@ -10960,8 +10953,8 @@
       <c r="H79" t="n">
         <v>0.1402</v>
       </c>
-      <c r="I79" t="e">
-        <v>#N/A</v>
+      <c r="I79" t="n">
+        <v>0.004</v>
       </c>
       <c r="J79" t="e">
         <v>#N/A</v>
@@ -10978,8 +10971,8 @@
       <c r="N79" t="n">
         <v>-23.9</v>
       </c>
-      <c r="O79" t="e">
-        <v>#N/A</v>
+      <c r="O79" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P79" t="e">
         <v>#N/A</v>
@@ -10991,7 +10984,7 @@
         <v>8.5</v>
       </c>
       <c r="S79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T79" t="e">
         <v>#N/A</v>
@@ -11008,29 +11001,29 @@
       <c r="X79" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z79" t="e">
-        <v>#N/A</v>
+      <c r="Y79" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA79" t="s">
         <v>281</v>
       </c>
-      <c r="AB79" t="e">
-        <v>#N/A</v>
+      <c r="AB79" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC79" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF79" t="e">
-        <v>#N/A</v>
+      <c r="AD79" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG79" t="e">
         <v>#N/A</v>
@@ -11052,7 +11045,7 @@
       <c r="B80" t="s">
         <v>271</v>
       </c>
-      <c r="C80" s="34" t="s">
+      <c r="C80" t="s">
         <v>272</v>
       </c>
       <c r="D80" t="s">
@@ -11070,8 +11063,8 @@
       <c r="H80" t="n">
         <v>0.1481</v>
       </c>
-      <c r="I80" t="e">
-        <v>#N/A</v>
+      <c r="I80" t="n">
+        <v>0.004</v>
       </c>
       <c r="J80" t="e">
         <v>#N/A</v>
@@ -11088,8 +11081,8 @@
       <c r="N80" t="n">
         <v>-22.7</v>
       </c>
-      <c r="O80" t="e">
-        <v>#N/A</v>
+      <c r="O80" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P80" t="e">
         <v>#N/A</v>
@@ -11101,7 +11094,7 @@
         <v>8.6</v>
       </c>
       <c r="S80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T80" t="e">
         <v>#N/A</v>
@@ -11118,29 +11111,29 @@
       <c r="X80" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z80" t="e">
-        <v>#N/A</v>
+      <c r="Y80" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA80" t="s">
         <v>281</v>
       </c>
-      <c r="AB80" t="e">
-        <v>#N/A</v>
+      <c r="AB80" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC80" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF80" t="e">
-        <v>#N/A</v>
+      <c r="AD80" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG80" t="e">
         <v>#N/A</v>
@@ -11162,7 +11155,7 @@
       <c r="B81" t="s">
         <v>271</v>
       </c>
-      <c r="C81" s="34" t="s">
+      <c r="C81" t="s">
         <v>272</v>
       </c>
       <c r="D81" t="s">
@@ -11180,8 +11173,8 @@
       <c r="H81" t="n">
         <v>0.149</v>
       </c>
-      <c r="I81" t="e">
-        <v>#N/A</v>
+      <c r="I81" t="n">
+        <v>0.004</v>
       </c>
       <c r="J81" t="e">
         <v>#N/A</v>
@@ -11198,8 +11191,8 @@
       <c r="N81" t="n">
         <v>-24.8</v>
       </c>
-      <c r="O81" t="e">
-        <v>#N/A</v>
+      <c r="O81" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P81" t="e">
         <v>#N/A</v>
@@ -11211,7 +11204,7 @@
         <v>9.2</v>
       </c>
       <c r="S81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T81" t="e">
         <v>#N/A</v>
@@ -11228,29 +11221,29 @@
       <c r="X81" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z81" t="e">
-        <v>#N/A</v>
+      <c r="Y81" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA81" t="s">
         <v>281</v>
       </c>
-      <c r="AB81" t="e">
-        <v>#N/A</v>
+      <c r="AB81" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC81" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF81" t="e">
-        <v>#N/A</v>
+      <c r="AD81" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG81" t="e">
         <v>#N/A</v>
@@ -11272,7 +11265,7 @@
       <c r="B82" t="s">
         <v>271</v>
       </c>
-      <c r="C82" s="34" t="s">
+      <c r="C82" t="s">
         <v>272</v>
       </c>
       <c r="D82" t="s">
@@ -11290,8 +11283,8 @@
       <c r="H82" t="n">
         <v>0.1496</v>
       </c>
-      <c r="I82" t="e">
-        <v>#N/A</v>
+      <c r="I82" t="n">
+        <v>0.004</v>
       </c>
       <c r="J82" t="e">
         <v>#N/A</v>
@@ -11308,8 +11301,8 @@
       <c r="N82" t="n">
         <v>-25.2</v>
       </c>
-      <c r="O82" t="e">
-        <v>#N/A</v>
+      <c r="O82" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P82" t="e">
         <v>#N/A</v>
@@ -11321,7 +11314,7 @@
         <v>9.3</v>
       </c>
       <c r="S82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T82" t="e">
         <v>#N/A</v>
@@ -11338,29 +11331,29 @@
       <c r="X82" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z82" t="e">
-        <v>#N/A</v>
+      <c r="Y82" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA82" t="s">
         <v>281</v>
       </c>
-      <c r="AB82" t="e">
-        <v>#N/A</v>
+      <c r="AB82" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC82" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF82" t="e">
-        <v>#N/A</v>
+      <c r="AD82" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG82" t="e">
         <v>#N/A</v>
@@ -11382,7 +11375,7 @@
       <c r="B83" t="s">
         <v>271</v>
       </c>
-      <c r="C83" s="34" t="s">
+      <c r="C83" t="s">
         <v>272</v>
       </c>
       <c r="D83" t="s">
@@ -11400,8 +11393,8 @@
       <c r="H83" t="n">
         <v>0.1513</v>
       </c>
-      <c r="I83" t="e">
-        <v>#N/A</v>
+      <c r="I83" t="n">
+        <v>0.004</v>
       </c>
       <c r="J83" t="e">
         <v>#N/A</v>
@@ -11418,8 +11411,8 @@
       <c r="N83" t="n">
         <v>-25</v>
       </c>
-      <c r="O83" t="e">
-        <v>#N/A</v>
+      <c r="O83" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P83" t="e">
         <v>#N/A</v>
@@ -11431,7 +11424,7 @@
         <v>7.6</v>
       </c>
       <c r="S83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T83" t="e">
         <v>#N/A</v>
@@ -11448,29 +11441,29 @@
       <c r="X83" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z83" t="e">
-        <v>#N/A</v>
+      <c r="Y83" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA83" t="s">
         <v>281</v>
       </c>
-      <c r="AB83" t="e">
-        <v>#N/A</v>
+      <c r="AB83" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC83" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF83" t="e">
-        <v>#N/A</v>
+      <c r="AD83" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG83" t="e">
         <v>#N/A</v>
@@ -11492,7 +11485,7 @@
       <c r="B84" t="s">
         <v>271</v>
       </c>
-      <c r="C84" s="34" t="s">
+      <c r="C84" t="s">
         <v>272</v>
       </c>
       <c r="D84" t="s">
@@ -11510,8 +11503,8 @@
       <c r="H84" t="n">
         <v>0.1522</v>
       </c>
-      <c r="I84" t="e">
-        <v>#N/A</v>
+      <c r="I84" t="n">
+        <v>0.004</v>
       </c>
       <c r="J84" t="e">
         <v>#N/A</v>
@@ -11528,8 +11521,8 @@
       <c r="N84" t="n">
         <v>-23.7</v>
       </c>
-      <c r="O84" t="e">
-        <v>#N/A</v>
+      <c r="O84" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P84" t="e">
         <v>#N/A</v>
@@ -11541,7 +11534,7 @@
         <v>11.4</v>
       </c>
       <c r="S84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T84" t="e">
         <v>#N/A</v>
@@ -11558,29 +11551,29 @@
       <c r="X84" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z84" t="e">
-        <v>#N/A</v>
+      <c r="Y84" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA84" t="s">
         <v>281</v>
       </c>
-      <c r="AB84" t="e">
-        <v>#N/A</v>
+      <c r="AB84" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC84" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF84" t="e">
-        <v>#N/A</v>
+      <c r="AD84" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG84" t="e">
         <v>#N/A</v>
@@ -11602,7 +11595,7 @@
       <c r="B85" t="s">
         <v>271</v>
       </c>
-      <c r="C85" s="34" t="s">
+      <c r="C85" t="s">
         <v>272</v>
       </c>
       <c r="D85" t="s">
@@ -11620,8 +11613,8 @@
       <c r="H85" t="n">
         <v>0.1531</v>
       </c>
-      <c r="I85" t="e">
-        <v>#N/A</v>
+      <c r="I85" t="n">
+        <v>0.004</v>
       </c>
       <c r="J85" t="e">
         <v>#N/A</v>
@@ -11638,8 +11631,8 @@
       <c r="N85" t="n">
         <v>-24.9</v>
       </c>
-      <c r="O85" t="e">
-        <v>#N/A</v>
+      <c r="O85" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P85" t="e">
         <v>#N/A</v>
@@ -11651,7 +11644,7 @@
         <v>8.8</v>
       </c>
       <c r="S85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T85" t="e">
         <v>#N/A</v>
@@ -11668,29 +11661,29 @@
       <c r="X85" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y85" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z85" t="e">
-        <v>#N/A</v>
+      <c r="Y85" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA85" t="s">
         <v>281</v>
       </c>
-      <c r="AB85" t="e">
-        <v>#N/A</v>
+      <c r="AB85" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC85" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD85" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE85" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF85" t="e">
-        <v>#N/A</v>
+      <c r="AD85" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG85" t="e">
         <v>#N/A</v>
@@ -11712,7 +11705,7 @@
       <c r="B86" t="s">
         <v>271</v>
       </c>
-      <c r="C86" s="34" t="s">
+      <c r="C86" t="s">
         <v>272</v>
       </c>
       <c r="D86" t="s">
@@ -11730,8 +11723,8 @@
       <c r="H86" t="n">
         <v>0.154</v>
       </c>
-      <c r="I86" t="e">
-        <v>#N/A</v>
+      <c r="I86" t="n">
+        <v>0.004</v>
       </c>
       <c r="J86" t="e">
         <v>#N/A</v>
@@ -11748,8 +11741,8 @@
       <c r="N86" t="n">
         <v>-24.2</v>
       </c>
-      <c r="O86" t="e">
-        <v>#N/A</v>
+      <c r="O86" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P86" t="e">
         <v>#N/A</v>
@@ -11761,7 +11754,7 @@
         <v>9.1</v>
       </c>
       <c r="S86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T86" t="e">
         <v>#N/A</v>
@@ -11778,29 +11771,29 @@
       <c r="X86" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y86" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z86" t="e">
-        <v>#N/A</v>
+      <c r="Y86" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA86" t="s">
         <v>281</v>
       </c>
-      <c r="AB86" t="e">
-        <v>#N/A</v>
+      <c r="AB86" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC86" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD86" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE86" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF86" t="e">
-        <v>#N/A</v>
+      <c r="AD86" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG86" t="e">
         <v>#N/A</v>
@@ -11822,7 +11815,7 @@
       <c r="B87" t="s">
         <v>271</v>
       </c>
-      <c r="C87" s="34" t="s">
+      <c r="C87" t="s">
         <v>272</v>
       </c>
       <c r="D87" t="s">
@@ -11840,8 +11833,8 @@
       <c r="H87" t="n">
         <v>0.1548</v>
       </c>
-      <c r="I87" t="e">
-        <v>#N/A</v>
+      <c r="I87" t="n">
+        <v>0.004</v>
       </c>
       <c r="J87" t="e">
         <v>#N/A</v>
@@ -11858,8 +11851,8 @@
       <c r="N87" t="n">
         <v>-24.7</v>
       </c>
-      <c r="O87" t="e">
-        <v>#N/A</v>
+      <c r="O87" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P87" t="e">
         <v>#N/A</v>
@@ -11871,7 +11864,7 @@
         <v>7.6</v>
       </c>
       <c r="S87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T87" t="e">
         <v>#N/A</v>
@@ -11888,29 +11881,29 @@
       <c r="X87" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y87" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z87" t="e">
-        <v>#N/A</v>
+      <c r="Y87" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA87" t="s">
         <v>281</v>
       </c>
-      <c r="AB87" t="e">
-        <v>#N/A</v>
+      <c r="AB87" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC87" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD87" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE87" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF87" t="e">
-        <v>#N/A</v>
+      <c r="AD87" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG87" t="e">
         <v>#N/A</v>
@@ -11932,7 +11925,7 @@
       <c r="B88" t="s">
         <v>271</v>
       </c>
-      <c r="C88" s="34" t="s">
+      <c r="C88" t="s">
         <v>272</v>
       </c>
       <c r="D88" t="s">
@@ -11950,8 +11943,8 @@
       <c r="H88" t="n">
         <v>0.1557</v>
       </c>
-      <c r="I88" t="e">
-        <v>#N/A</v>
+      <c r="I88" t="n">
+        <v>0.004</v>
       </c>
       <c r="J88" t="e">
         <v>#N/A</v>
@@ -11968,8 +11961,8 @@
       <c r="N88" t="n">
         <v>-25.4</v>
       </c>
-      <c r="O88" t="e">
-        <v>#N/A</v>
+      <c r="O88" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P88" t="e">
         <v>#N/A</v>
@@ -11981,7 +11974,7 @@
         <v>7.4</v>
       </c>
       <c r="S88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T88" t="e">
         <v>#N/A</v>
@@ -11998,29 +11991,29 @@
       <c r="X88" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y88" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z88" t="e">
-        <v>#N/A</v>
+      <c r="Y88" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA88" t="s">
         <v>281</v>
       </c>
-      <c r="AB88" t="e">
-        <v>#N/A</v>
+      <c r="AB88" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC88" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD88" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE88" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF88" t="e">
-        <v>#N/A</v>
+      <c r="AD88" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG88" t="e">
         <v>#N/A</v>
@@ -12042,7 +12035,7 @@
       <c r="B89" t="s">
         <v>271</v>
       </c>
-      <c r="C89" s="34" t="s">
+      <c r="C89" t="s">
         <v>272</v>
       </c>
       <c r="D89" t="s">
@@ -12060,8 +12053,8 @@
       <c r="H89" t="n">
         <v>0.1566</v>
       </c>
-      <c r="I89" t="e">
-        <v>#N/A</v>
+      <c r="I89" t="n">
+        <v>0.004</v>
       </c>
       <c r="J89" t="e">
         <v>#N/A</v>
@@ -12078,8 +12071,8 @@
       <c r="N89" t="n">
         <v>-24.6</v>
       </c>
-      <c r="O89" t="e">
-        <v>#N/A</v>
+      <c r="O89" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P89" t="e">
         <v>#N/A</v>
@@ -12091,7 +12084,7 @@
         <v>8.4</v>
       </c>
       <c r="S89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T89" t="e">
         <v>#N/A</v>
@@ -12108,29 +12101,29 @@
       <c r="X89" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y89" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z89" t="e">
-        <v>#N/A</v>
+      <c r="Y89" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA89" t="s">
         <v>281</v>
       </c>
-      <c r="AB89" t="e">
-        <v>#N/A</v>
+      <c r="AB89" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC89" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD89" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE89" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF89" t="e">
-        <v>#N/A</v>
+      <c r="AD89" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG89" t="e">
         <v>#N/A</v>
@@ -12152,7 +12145,7 @@
       <c r="B90" t="s">
         <v>271</v>
       </c>
-      <c r="C90" s="34" t="s">
+      <c r="C90" t="s">
         <v>272</v>
       </c>
       <c r="D90" t="s">
@@ -12170,8 +12163,8 @@
       <c r="H90" t="n">
         <v>0.1575</v>
       </c>
-      <c r="I90" t="e">
-        <v>#N/A</v>
+      <c r="I90" t="n">
+        <v>0.004</v>
       </c>
       <c r="J90" t="e">
         <v>#N/A</v>
@@ -12188,8 +12181,8 @@
       <c r="N90" t="n">
         <v>-24.4</v>
       </c>
-      <c r="O90" t="e">
-        <v>#N/A</v>
+      <c r="O90" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P90" t="e">
         <v>#N/A</v>
@@ -12201,7 +12194,7 @@
         <v>8.6</v>
       </c>
       <c r="S90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T90" t="e">
         <v>#N/A</v>
@@ -12218,29 +12211,29 @@
       <c r="X90" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y90" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z90" t="e">
-        <v>#N/A</v>
+      <c r="Y90" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA90" t="s">
         <v>281</v>
       </c>
-      <c r="AB90" t="e">
-        <v>#N/A</v>
+      <c r="AB90" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC90" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD90" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE90" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF90" t="e">
-        <v>#N/A</v>
+      <c r="AD90" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG90" t="e">
         <v>#N/A</v>
@@ -12262,7 +12255,7 @@
       <c r="B91" t="s">
         <v>271</v>
       </c>
-      <c r="C91" s="34" t="s">
+      <c r="C91" t="s">
         <v>272</v>
       </c>
       <c r="D91" t="s">
@@ -12280,8 +12273,8 @@
       <c r="H91" t="n">
         <v>0.1584</v>
       </c>
-      <c r="I91" t="e">
-        <v>#N/A</v>
+      <c r="I91" t="n">
+        <v>0.004</v>
       </c>
       <c r="J91" t="e">
         <v>#N/A</v>
@@ -12298,8 +12291,8 @@
       <c r="N91" t="n">
         <v>-24.7</v>
       </c>
-      <c r="O91" t="e">
-        <v>#N/A</v>
+      <c r="O91" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P91" t="e">
         <v>#N/A</v>
@@ -12311,7 +12304,7 @@
         <v>10.6</v>
       </c>
       <c r="S91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T91" t="e">
         <v>#N/A</v>
@@ -12328,29 +12321,29 @@
       <c r="X91" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y91" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z91" t="e">
-        <v>#N/A</v>
+      <c r="Y91" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA91" t="s">
         <v>281</v>
       </c>
-      <c r="AB91" t="e">
-        <v>#N/A</v>
+      <c r="AB91" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC91" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD91" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE91" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF91" t="e">
-        <v>#N/A</v>
+      <c r="AD91" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG91" t="e">
         <v>#N/A</v>
@@ -12372,7 +12365,7 @@
       <c r="B92" t="s">
         <v>271</v>
       </c>
-      <c r="C92" s="34" t="s">
+      <c r="C92" t="s">
         <v>272</v>
       </c>
       <c r="D92" t="s">
@@ -12390,8 +12383,8 @@
       <c r="H92" t="n">
         <v>0.1592</v>
       </c>
-      <c r="I92" t="e">
-        <v>#N/A</v>
+      <c r="I92" t="n">
+        <v>0.004</v>
       </c>
       <c r="J92" t="e">
         <v>#N/A</v>
@@ -12408,8 +12401,8 @@
       <c r="N92" t="n">
         <v>-24.1</v>
       </c>
-      <c r="O92" t="e">
-        <v>#N/A</v>
+      <c r="O92" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P92" t="e">
         <v>#N/A</v>
@@ -12421,7 +12414,7 @@
         <v>9.1</v>
       </c>
       <c r="S92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T92" t="e">
         <v>#N/A</v>
@@ -12438,29 +12431,29 @@
       <c r="X92" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y92" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z92" t="e">
-        <v>#N/A</v>
+      <c r="Y92" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA92" t="s">
         <v>281</v>
       </c>
-      <c r="AB92" t="e">
-        <v>#N/A</v>
+      <c r="AB92" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC92" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD92" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE92" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF92" t="e">
-        <v>#N/A</v>
+      <c r="AD92" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG92" t="e">
         <v>#N/A</v>
@@ -12482,7 +12475,7 @@
       <c r="B93" t="s">
         <v>271</v>
       </c>
-      <c r="C93" s="34" t="s">
+      <c r="C93" t="s">
         <v>272</v>
       </c>
       <c r="D93" t="s">
@@ -12500,8 +12493,8 @@
       <c r="H93" t="n">
         <v>0.1645</v>
       </c>
-      <c r="I93" t="e">
-        <v>#N/A</v>
+      <c r="I93" t="n">
+        <v>0.004</v>
       </c>
       <c r="J93" t="e">
         <v>#N/A</v>
@@ -12518,8 +12511,8 @@
       <c r="N93" t="n">
         <v>-22.9</v>
       </c>
-      <c r="O93" t="e">
-        <v>#N/A</v>
+      <c r="O93" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P93" t="e">
         <v>#N/A</v>
@@ -12531,7 +12524,7 @@
         <v>10.1</v>
       </c>
       <c r="S93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T93" t="e">
         <v>#N/A</v>
@@ -12548,29 +12541,29 @@
       <c r="X93" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y93" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z93" t="e">
-        <v>#N/A</v>
+      <c r="Y93" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA93" t="s">
         <v>281</v>
       </c>
-      <c r="AB93" t="e">
-        <v>#N/A</v>
+      <c r="AB93" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC93" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD93" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE93" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF93" t="e">
-        <v>#N/A</v>
+      <c r="AD93" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG93" t="e">
         <v>#N/A</v>
@@ -12592,7 +12585,7 @@
       <c r="B94" t="s">
         <v>271</v>
       </c>
-      <c r="C94" s="34" t="s">
+      <c r="C94" t="s">
         <v>272</v>
       </c>
       <c r="D94" t="s">
@@ -12610,8 +12603,8 @@
       <c r="H94" t="n">
         <v>0.168</v>
       </c>
-      <c r="I94" t="e">
-        <v>#N/A</v>
+      <c r="I94" t="n">
+        <v>0.004</v>
       </c>
       <c r="J94" t="e">
         <v>#N/A</v>
@@ -12628,8 +12621,8 @@
       <c r="N94" t="n">
         <v>-23</v>
       </c>
-      <c r="O94" t="e">
-        <v>#N/A</v>
+      <c r="O94" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P94" t="e">
         <v>#N/A</v>
@@ -12641,7 +12634,7 @@
         <v>12.9</v>
       </c>
       <c r="S94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T94" t="e">
         <v>#N/A</v>
@@ -12658,29 +12651,29 @@
       <c r="X94" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z94" t="e">
-        <v>#N/A</v>
+      <c r="Y94" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA94" t="s">
         <v>281</v>
       </c>
-      <c r="AB94" t="e">
-        <v>#N/A</v>
+      <c r="AB94" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC94" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF94" t="e">
-        <v>#N/A</v>
+      <c r="AD94" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG94" t="e">
         <v>#N/A</v>
@@ -12702,7 +12695,7 @@
       <c r="B95" t="s">
         <v>271</v>
       </c>
-      <c r="C95" s="34" t="s">
+      <c r="C95" t="s">
         <v>272</v>
       </c>
       <c r="D95" t="s">
@@ -12720,8 +12713,8 @@
       <c r="H95" t="n">
         <v>0.1698</v>
       </c>
-      <c r="I95" t="e">
-        <v>#N/A</v>
+      <c r="I95" t="n">
+        <v>0.004</v>
       </c>
       <c r="J95" t="e">
         <v>#N/A</v>
@@ -12738,8 +12731,8 @@
       <c r="N95" t="n">
         <v>-23.2</v>
       </c>
-      <c r="O95" t="e">
-        <v>#N/A</v>
+      <c r="O95" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P95" t="e">
         <v>#N/A</v>
@@ -12751,7 +12744,7 @@
         <v>11.2</v>
       </c>
       <c r="S95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T95" t="e">
         <v>#N/A</v>
@@ -12768,29 +12761,29 @@
       <c r="X95" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y95" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z95" t="e">
-        <v>#N/A</v>
+      <c r="Y95" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA95" t="s">
         <v>281</v>
       </c>
-      <c r="AB95" t="e">
-        <v>#N/A</v>
+      <c r="AB95" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC95" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD95" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE95" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF95" t="e">
-        <v>#N/A</v>
+      <c r="AD95" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG95" t="e">
         <v>#N/A</v>
@@ -12812,7 +12805,7 @@
       <c r="B96" t="s">
         <v>271</v>
       </c>
-      <c r="C96" s="34" t="s">
+      <c r="C96" t="s">
         <v>272</v>
       </c>
       <c r="D96" t="s">
@@ -12830,8 +12823,8 @@
       <c r="H96" t="n">
         <v>0.1716</v>
       </c>
-      <c r="I96" t="e">
-        <v>#N/A</v>
+      <c r="I96" t="n">
+        <v>0.004</v>
       </c>
       <c r="J96" t="e">
         <v>#N/A</v>
@@ -12848,8 +12841,8 @@
       <c r="N96" t="n">
         <v>-22.3</v>
       </c>
-      <c r="O96" t="e">
-        <v>#N/A</v>
+      <c r="O96" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P96" t="e">
         <v>#N/A</v>
@@ -12861,7 +12854,7 @@
         <v>11.6</v>
       </c>
       <c r="S96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T96" t="e">
         <v>#N/A</v>
@@ -12878,29 +12871,29 @@
       <c r="X96" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y96" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z96" t="e">
-        <v>#N/A</v>
+      <c r="Y96" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA96" t="s">
         <v>281</v>
       </c>
-      <c r="AB96" t="e">
-        <v>#N/A</v>
+      <c r="AB96" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC96" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD96" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE96" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF96" t="e">
-        <v>#N/A</v>
+      <c r="AD96" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG96" t="e">
         <v>#N/A</v>
@@ -12922,7 +12915,7 @@
       <c r="B97" t="s">
         <v>271</v>
       </c>
-      <c r="C97" s="34" t="s">
+      <c r="C97" t="s">
         <v>272</v>
       </c>
       <c r="D97" t="s">
@@ -12940,8 +12933,8 @@
       <c r="H97" t="n">
         <v>0.1733</v>
       </c>
-      <c r="I97" t="e">
-        <v>#N/A</v>
+      <c r="I97" t="n">
+        <v>0.004</v>
       </c>
       <c r="J97" t="e">
         <v>#N/A</v>
@@ -12958,8 +12951,8 @@
       <c r="N97" t="n">
         <v>-23.1</v>
       </c>
-      <c r="O97" t="e">
-        <v>#N/A</v>
+      <c r="O97" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P97" t="e">
         <v>#N/A</v>
@@ -12971,7 +12964,7 @@
         <v>12.7</v>
       </c>
       <c r="S97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T97" t="e">
         <v>#N/A</v>
@@ -12988,29 +12981,29 @@
       <c r="X97" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y97" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z97" t="e">
-        <v>#N/A</v>
+      <c r="Y97" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA97" t="s">
         <v>281</v>
       </c>
-      <c r="AB97" t="e">
-        <v>#N/A</v>
+      <c r="AB97" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC97" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD97" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE97" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF97" t="e">
-        <v>#N/A</v>
+      <c r="AD97" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG97" t="e">
         <v>#N/A</v>
@@ -13032,7 +13025,7 @@
       <c r="B98" t="s">
         <v>271</v>
       </c>
-      <c r="C98" s="34" t="s">
+      <c r="C98" t="s">
         <v>272</v>
       </c>
       <c r="D98" t="s">
@@ -13050,8 +13043,8 @@
       <c r="H98" t="n">
         <v>0.1751</v>
       </c>
-      <c r="I98" t="e">
-        <v>#N/A</v>
+      <c r="I98" t="n">
+        <v>0.004</v>
       </c>
       <c r="J98" t="e">
         <v>#N/A</v>
@@ -13068,8 +13061,8 @@
       <c r="N98" t="n">
         <v>-21.7</v>
       </c>
-      <c r="O98" t="e">
-        <v>#N/A</v>
+      <c r="O98" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P98" t="e">
         <v>#N/A</v>
@@ -13081,7 +13074,7 @@
         <v>12.4</v>
       </c>
       <c r="S98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T98" t="e">
         <v>#N/A</v>
@@ -13098,29 +13091,29 @@
       <c r="X98" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y98" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z98" t="e">
-        <v>#N/A</v>
+      <c r="Y98" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA98" t="s">
         <v>281</v>
       </c>
-      <c r="AB98" t="e">
-        <v>#N/A</v>
+      <c r="AB98" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC98" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD98" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE98" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF98" t="e">
-        <v>#N/A</v>
+      <c r="AD98" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG98" t="e">
         <v>#N/A</v>
@@ -13142,7 +13135,7 @@
       <c r="B99" t="s">
         <v>271</v>
       </c>
-      <c r="C99" s="34" t="s">
+      <c r="C99" t="s">
         <v>272</v>
       </c>
       <c r="D99" t="s">
@@ -13160,8 +13153,8 @@
       <c r="H99" t="n">
         <v>0.1768</v>
       </c>
-      <c r="I99" t="e">
-        <v>#N/A</v>
+      <c r="I99" t="n">
+        <v>0.004</v>
       </c>
       <c r="J99" t="e">
         <v>#N/A</v>
@@ -13178,8 +13171,8 @@
       <c r="N99" t="n">
         <v>-23</v>
       </c>
-      <c r="O99" t="e">
-        <v>#N/A</v>
+      <c r="O99" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P99" t="e">
         <v>#N/A</v>
@@ -13191,7 +13184,7 @@
         <v>12.1</v>
       </c>
       <c r="S99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T99" t="e">
         <v>#N/A</v>
@@ -13208,29 +13201,29 @@
       <c r="X99" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z99" t="e">
-        <v>#N/A</v>
+      <c r="Y99" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA99" t="s">
         <v>281</v>
       </c>
-      <c r="AB99" t="e">
-        <v>#N/A</v>
+      <c r="AB99" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC99" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF99" t="e">
-        <v>#N/A</v>
+      <c r="AD99" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG99" t="e">
         <v>#N/A</v>
@@ -13252,7 +13245,7 @@
       <c r="B100" t="s">
         <v>271</v>
       </c>
-      <c r="C100" s="34" t="s">
+      <c r="C100" t="s">
         <v>272</v>
       </c>
       <c r="D100" t="s">
@@ -13270,8 +13263,8 @@
       <c r="H100" t="n">
         <v>0.1786</v>
       </c>
-      <c r="I100" t="e">
-        <v>#N/A</v>
+      <c r="I100" t="n">
+        <v>0.004</v>
       </c>
       <c r="J100" t="e">
         <v>#N/A</v>
@@ -13288,8 +13281,8 @@
       <c r="N100" t="n">
         <v>-22.6</v>
       </c>
-      <c r="O100" t="e">
-        <v>#N/A</v>
+      <c r="O100" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P100" t="e">
         <v>#N/A</v>
@@ -13301,7 +13294,7 @@
         <v>11.9</v>
       </c>
       <c r="S100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T100" t="e">
         <v>#N/A</v>
@@ -13318,29 +13311,29 @@
       <c r="X100" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z100" t="e">
-        <v>#N/A</v>
+      <c r="Y100" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA100" t="s">
         <v>281</v>
       </c>
-      <c r="AB100" t="e">
-        <v>#N/A</v>
+      <c r="AB100" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC100" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF100" t="e">
-        <v>#N/A</v>
+      <c r="AD100" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG100" t="e">
         <v>#N/A</v>
@@ -13362,7 +13355,7 @@
       <c r="B101" t="s">
         <v>271</v>
       </c>
-      <c r="C101" s="34" t="s">
+      <c r="C101" t="s">
         <v>272</v>
       </c>
       <c r="D101" t="s">
@@ -13380,8 +13373,8 @@
       <c r="H101" t="n">
         <v>0.1804</v>
       </c>
-      <c r="I101" t="e">
-        <v>#N/A</v>
+      <c r="I101" t="n">
+        <v>0.004</v>
       </c>
       <c r="J101" t="e">
         <v>#N/A</v>
@@ -13398,8 +13391,8 @@
       <c r="N101" t="n">
         <v>-22.9</v>
       </c>
-      <c r="O101" t="e">
-        <v>#N/A</v>
+      <c r="O101" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P101" t="e">
         <v>#N/A</v>
@@ -13411,7 +13404,7 @@
         <v>13.3</v>
       </c>
       <c r="S101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T101" t="e">
         <v>#N/A</v>
@@ -13428,29 +13421,29 @@
       <c r="X101" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y101" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z101" t="e">
-        <v>#N/A</v>
+      <c r="Y101" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA101" t="s">
         <v>281</v>
       </c>
-      <c r="AB101" t="e">
-        <v>#N/A</v>
+      <c r="AB101" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC101" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD101" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE101" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF101" t="e">
-        <v>#N/A</v>
+      <c r="AD101" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG101" t="e">
         <v>#N/A</v>
@@ -13472,7 +13465,7 @@
       <c r="B102" t="s">
         <v>271</v>
       </c>
-      <c r="C102" s="34" t="s">
+      <c r="C102" t="s">
         <v>272</v>
       </c>
       <c r="D102" t="s">
@@ -13490,8 +13483,8 @@
       <c r="H102" t="n">
         <v>0.1821</v>
       </c>
-      <c r="I102" t="e">
-        <v>#N/A</v>
+      <c r="I102" t="n">
+        <v>0.004</v>
       </c>
       <c r="J102" t="e">
         <v>#N/A</v>
@@ -13508,8 +13501,8 @@
       <c r="N102" t="n">
         <v>-22.4</v>
       </c>
-      <c r="O102" t="e">
-        <v>#N/A</v>
+      <c r="O102" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P102" t="e">
         <v>#N/A</v>
@@ -13521,7 +13514,7 @@
         <v>12.4</v>
       </c>
       <c r="S102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T102" t="e">
         <v>#N/A</v>
@@ -13538,29 +13531,29 @@
       <c r="X102" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y102" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z102" t="e">
-        <v>#N/A</v>
+      <c r="Y102" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA102" t="s">
         <v>281</v>
       </c>
-      <c r="AB102" t="e">
-        <v>#N/A</v>
+      <c r="AB102" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC102" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD102" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE102" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF102" t="e">
-        <v>#N/A</v>
+      <c r="AD102" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG102" t="e">
         <v>#N/A</v>
@@ -13582,7 +13575,7 @@
       <c r="B103" t="s">
         <v>271</v>
       </c>
-      <c r="C103" s="34" t="s">
+      <c r="C103" t="s">
         <v>272</v>
       </c>
       <c r="D103" t="s">
@@ -13600,8 +13593,8 @@
       <c r="H103" t="n">
         <v>0.1856</v>
       </c>
-      <c r="I103" t="e">
-        <v>#N/A</v>
+      <c r="I103" t="n">
+        <v>0.004</v>
       </c>
       <c r="J103" t="e">
         <v>#N/A</v>
@@ -13618,8 +13611,8 @@
       <c r="N103" t="n">
         <v>-22</v>
       </c>
-      <c r="O103" t="e">
-        <v>#N/A</v>
+      <c r="O103" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P103" t="e">
         <v>#N/A</v>
@@ -13631,7 +13624,7 @@
         <v>14.4</v>
       </c>
       <c r="S103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T103" t="e">
         <v>#N/A</v>
@@ -13648,29 +13641,29 @@
       <c r="X103" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y103" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z103" t="e">
-        <v>#N/A</v>
+      <c r="Y103" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA103" t="s">
         <v>281</v>
       </c>
-      <c r="AB103" t="e">
-        <v>#N/A</v>
+      <c r="AB103" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC103" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD103" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE103" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF103" t="e">
-        <v>#N/A</v>
+      <c r="AD103" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG103" t="e">
         <v>#N/A</v>
@@ -13692,7 +13685,7 @@
       <c r="B104" t="s">
         <v>271</v>
       </c>
-      <c r="C104" s="34" t="s">
+      <c r="C104" t="s">
         <v>272</v>
       </c>
       <c r="D104" t="s">
@@ -13710,8 +13703,8 @@
       <c r="H104" t="n">
         <v>0.1865</v>
       </c>
-      <c r="I104" t="e">
-        <v>#N/A</v>
+      <c r="I104" t="n">
+        <v>0.004</v>
       </c>
       <c r="J104" t="e">
         <v>#N/A</v>
@@ -13728,8 +13721,8 @@
       <c r="N104" t="n">
         <v>-22.2</v>
       </c>
-      <c r="O104" t="e">
-        <v>#N/A</v>
+      <c r="O104" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P104" t="e">
         <v>#N/A</v>
@@ -13741,7 +13734,7 @@
         <v>13.2</v>
       </c>
       <c r="S104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T104" t="e">
         <v>#N/A</v>
@@ -13758,29 +13751,29 @@
       <c r="X104" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y104" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z104" t="e">
-        <v>#N/A</v>
+      <c r="Y104" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA104" t="s">
         <v>281</v>
       </c>
-      <c r="AB104" t="e">
-        <v>#N/A</v>
+      <c r="AB104" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC104" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD104" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE104" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF104" t="e">
-        <v>#N/A</v>
+      <c r="AD104" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG104" t="e">
         <v>#N/A</v>
@@ -13802,7 +13795,7 @@
       <c r="B105" t="s">
         <v>271</v>
       </c>
-      <c r="C105" s="34" t="s">
+      <c r="C105" t="s">
         <v>272</v>
       </c>
       <c r="D105" t="s">
@@ -13820,8 +13813,8 @@
       <c r="H105" t="n">
         <v>0.1875</v>
       </c>
-      <c r="I105" t="e">
-        <v>#N/A</v>
+      <c r="I105" t="n">
+        <v>0.004</v>
       </c>
       <c r="J105" t="e">
         <v>#N/A</v>
@@ -13838,8 +13831,8 @@
       <c r="N105" t="n">
         <v>-21.9</v>
       </c>
-      <c r="O105" t="e">
-        <v>#N/A</v>
+      <c r="O105" t="n">
+        <v>0.707106781186547</v>
       </c>
       <c r="P105" t="e">
         <v>#N/A</v>
@@ -13851,7 +13844,7 @@
         <v>15.4</v>
       </c>
       <c r="S105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T105" t="e">
         <v>#N/A</v>
@@ -13868,29 +13861,29 @@
       <c r="X105" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y105" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z105" t="e">
-        <v>#N/A</v>
+      <c r="Y105" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>0.36</v>
       </c>
       <c r="AA105" t="s">
         <v>281</v>
       </c>
-      <c r="AB105" t="e">
-        <v>#N/A</v>
+      <c r="AB105" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC105" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD105" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE105" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF105" t="e">
-        <v>#N/A</v>
+      <c r="AD105" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG105" t="e">
         <v>#N/A</v>
@@ -13915,109 +13908,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-    <hyperlink ref="C37" r:id="rId33h"/>
-    <hyperlink ref="C38" r:id="rId34h"/>
-    <hyperlink ref="C39" r:id="rId35h"/>
-    <hyperlink ref="C40" r:id="rId36h"/>
-    <hyperlink ref="C41" r:id="rId37h"/>
-    <hyperlink ref="C42" r:id="rId38h"/>
-    <hyperlink ref="C43" r:id="rId39h"/>
-    <hyperlink ref="C44" r:id="rId40h"/>
-    <hyperlink ref="C45" r:id="rId41h"/>
-    <hyperlink ref="C46" r:id="rId42h"/>
-    <hyperlink ref="C47" r:id="rId43h"/>
-    <hyperlink ref="C48" r:id="rId44h"/>
-    <hyperlink ref="C49" r:id="rId45h"/>
-    <hyperlink ref="C50" r:id="rId46h"/>
-    <hyperlink ref="C51" r:id="rId47h"/>
-    <hyperlink ref="C52" r:id="rId48h"/>
-    <hyperlink ref="C53" r:id="rId49h"/>
-    <hyperlink ref="C54" r:id="rId50h"/>
-    <hyperlink ref="C55" r:id="rId51h"/>
-    <hyperlink ref="C56" r:id="rId52h"/>
-    <hyperlink ref="C57" r:id="rId53h"/>
-    <hyperlink ref="C58" r:id="rId54h"/>
-    <hyperlink ref="C59" r:id="rId55h"/>
-    <hyperlink ref="C60" r:id="rId56h"/>
-    <hyperlink ref="C61" r:id="rId57h"/>
-    <hyperlink ref="C62" r:id="rId58h"/>
-    <hyperlink ref="C63" r:id="rId59h"/>
-    <hyperlink ref="C64" r:id="rId60h"/>
-    <hyperlink ref="C65" r:id="rId61h"/>
-    <hyperlink ref="C66" r:id="rId62h"/>
-    <hyperlink ref="C67" r:id="rId63h"/>
-    <hyperlink ref="C68" r:id="rId64h"/>
-    <hyperlink ref="C69" r:id="rId65h"/>
-    <hyperlink ref="C70" r:id="rId66h"/>
-    <hyperlink ref="C71" r:id="rId67h"/>
-    <hyperlink ref="C72" r:id="rId68h"/>
-    <hyperlink ref="C73" r:id="rId69h"/>
-    <hyperlink ref="C74" r:id="rId70h"/>
-    <hyperlink ref="C75" r:id="rId71h"/>
-    <hyperlink ref="C76" r:id="rId72h"/>
-    <hyperlink ref="C77" r:id="rId73h"/>
-    <hyperlink ref="C78" r:id="rId74h"/>
-    <hyperlink ref="C79" r:id="rId75h"/>
-    <hyperlink ref="C80" r:id="rId76h"/>
-    <hyperlink ref="C81" r:id="rId77h"/>
-    <hyperlink ref="C82" r:id="rId78h"/>
-    <hyperlink ref="C83" r:id="rId79h"/>
-    <hyperlink ref="C84" r:id="rId80h"/>
-    <hyperlink ref="C85" r:id="rId81h"/>
-    <hyperlink ref="C86" r:id="rId82h"/>
-    <hyperlink ref="C87" r:id="rId83h"/>
-    <hyperlink ref="C88" r:id="rId84h"/>
-    <hyperlink ref="C89" r:id="rId85h"/>
-    <hyperlink ref="C90" r:id="rId86h"/>
-    <hyperlink ref="C91" r:id="rId87h"/>
-    <hyperlink ref="C92" r:id="rId88h"/>
-    <hyperlink ref="C93" r:id="rId89h"/>
-    <hyperlink ref="C94" r:id="rId90h"/>
-    <hyperlink ref="C95" r:id="rId91h"/>
-    <hyperlink ref="C96" r:id="rId92h"/>
-    <hyperlink ref="C97" r:id="rId93h"/>
-    <hyperlink ref="C98" r:id="rId94h"/>
-    <hyperlink ref="C99" r:id="rId95h"/>
-    <hyperlink ref="C100" r:id="rId96h"/>
-    <hyperlink ref="C101" r:id="rId97h"/>
-    <hyperlink ref="C102" r:id="rId98h"/>
-    <hyperlink ref="C103" r:id="rId99h"/>
-    <hyperlink ref="C104" r:id="rId100h"/>
-    <hyperlink ref="C105" r:id="rId101h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
